--- a/xlsx/causal-autoimmune-architecture-platform.xlsx
+++ b/xlsx/causal-autoimmune-architecture-platform.xlsx
@@ -40,7 +40,8 @@
     <sheet name="StateTransitions" sheetId="33" r:id="rId34"/>
     <sheet name="SubjectStateInstances" sheetId="34" r:id="rId35"/>
     <sheet name="__meta__" sheetId="35" r:id="rId36"/>
-    <sheet name="_original_json" sheetId="36" r:id="rId37" state="hidden"/>
+    <sheet name="DiseaseDomainConcepts" sheetId="36" r:id="rId37"/>
+    <sheet name="_original_json" sheetId="37" r:id="rId38" state="hidden"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">__meta__!$A$1:$H$1</definedName>
@@ -51,6 +52,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">ClinicalPhenotypes!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">CohortReplications!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">CounterfactualTrajectories!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">DiseaseDomainConcepts!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DiseaseStages!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">EnvironmentalExposures!$A$1:$K$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">EpistaticInteractions!$A$1:$K$1</definedName>
@@ -5937,6 +5939,146 @@
 </comments>
 </file>
 
+<file path=xl/comments36.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">CMCC</d:author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Slug PK.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Disease this concept belongs to (SLE/RA/PsA/* for cross-cutting). Convention string, not a FK.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>deep-dag | schema | vocabulary — how deeply v2 models this concept.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>What the concept is and how v2 represents it.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Which TYPE of original-challenge stressor this concept instantiates (for the reconcile map).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Echoes ConceptLabel.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Path to this concept's page.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>TRUE when this concept carries a witnessed inference DAG (status = deep-dag).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>TRUE when first-class schema/data (deep-dag or schema).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Human-readable concept name (the audit's missing word).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -7220,7 +7362,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="1405">
   <si>
     <t>AutoimmuneDiseaseId</t>
   </si>
@@ -9553,6 +9695,69 @@
     <t>The skeptic's claim that a deterministic function over LLM-chosen inputs just launders a hallucination; defeated by externalized knobs + independent witness.</t>
   </si>
   <si>
+    <t>gt-disease-state-simulator</t>
+  </si>
+  <si>
+    <t>disease state simulator</t>
+  </si>
+  <si>
+    <t>The v2 layer the audit asked for: disease modeled as a WITNESSED state machine whose transitions fire only on raw longitudinal observations (rising anti-dsDNA, falling C3/C4, proteinuria). Current state and dwell-time are derived &amp; bitemporal — the contrast the audit drew with an 'evidence gate'.</t>
+  </si>
+  <si>
+    <t>gt-evidence-gate</t>
+  </si>
+  <si>
+    <t>evidence gate</t>
+  </si>
+  <si>
+    <t>The v1 layer: per-patient adjudication of whether a prediction is trustworthy enough to act on (the four gates + IsClinicallyActionable). v2 keeps this and adds the disease-state simulator above it on the same hub.</t>
+  </si>
+  <si>
+    <t>gt-disease-progression-machine</t>
+  </si>
+  <si>
+    <t>disease progression machine</t>
+  </si>
+  <si>
+    <t>A state machine on the polymorphic StateMachines substrate whose subject is a patient's disease course (presymptomatic -&gt; serologic-active -&gt; early-nephritis -&gt; renal-flare-risk -&gt; biopsy-indicated). Transitions are raw-leaf-triggered; current state is the derived IsCurrent occupancy.</t>
+  </si>
+  <si>
+    <t>gt-dwell-time</t>
+  </si>
+  <si>
+    <t>dwell time</t>
+  </si>
+  <si>
+    <t>Bitemporal derivation: how long a subject has been in a disease state (now - EnteredAt while current; ExitedAt - EnteredAt once left). The audit asked for 'how long has the patient/disease been in a state' — this is that, as a formula.</t>
+  </si>
+  <si>
+    <t>gt-serology-trajectory</t>
+  </si>
+  <si>
+    <t>serology trajectory</t>
+  </si>
+  <si>
+    <t>The raw longitudinal leaves driving progression: anti-dsDNA titre trend (rising/stable/falling), complement C3/C4 trend, proteinuria. The LLM/lab may emit these; everything above them is derived.</t>
+  </si>
+  <si>
+    <t>gt-treatment-line-recommendation</t>
+  </si>
+  <si>
+    <t>treatment line recommendation</t>
+  </si>
+  <si>
+    <t>Derived field: given the patient's confirmed causal mechanism + current disease state, the recommended therapy (MMF vs belimumab vs anifrolumab) and the single deciding reason. The audit's second worked example.</t>
+  </si>
+  <si>
+    <t>gt-corpus-discovery</t>
+  </si>
+  <si>
+    <t>corpus discovery</t>
+  </si>
+  <si>
+    <t>The cohort-level surface where causal-hypothesis patterns EMERGE across many patients (vs v1's per-patient verdicts). Discovery is inherently corpus-level; this is the v2 reframe of the audit's 'you don't do discovery' critique.</t>
+  </si>
+  <si>
     <t>LeopoldLoopId</t>
   </si>
   <si>
@@ -10991,6 +11196,342 @@
   </si>
   <si>
     <t>Total-coverage contract toggle: assert every DAG node linked to the patient down to ground truth contributes a fragment or a named suppression (tfs-report-covers-every-dag-node).</t>
+  </si>
+  <si>
+    <t>DiseaseDomainConceptId</t>
+  </si>
+  <si>
+    <t>ConceptLabel</t>
+  </si>
+  <si>
+    <t>RelatedDisease</t>
+  </si>
+  <si>
+    <t>ModelingStatus</t>
+  </si>
+  <si>
+    <t>ChallengeStressorType</t>
+  </si>
+  <si>
+    <t>IsDeeplyModeled</t>
+  </si>
+  <si>
+    <t>IsSchemaModeled</t>
+  </si>
+  <si>
+    <t>lupus-nephritis</t>
+  </si>
+  <si>
+    <t>Lupus Nephritis</t>
+  </si>
+  <si>
+    <t>SLE</t>
+  </si>
+  <si>
+    <t>deep-dag</t>
+  </si>
+  <si>
+    <t>Renal involvement of SLE; immune-complex glomerulonephritis. v2 models its PROGRESSION as a witnessed state machine driven by rising anti-dsDNA + falling complement + proteinuria.</t>
+  </si>
+  <si>
+    <t>disease-progression / organ-specific subtype</t>
+  </si>
+  <si>
+    <t>treatment-line-selection</t>
+  </si>
+  <si>
+    <t>Treatment-Line Selection</t>
+  </si>
+  <si>
+    <t>Which therapy to choose given the patient's causal mechanism + disease state: mycophenolate (MMF) vs belimumab vs anifrolumab. v2 derives a recommended line + single deciding reason.</t>
+  </si>
+  <si>
+    <t>treatment response / patient stratification</t>
+  </si>
+  <si>
+    <t>neuropsychiatric-lupus</t>
+  </si>
+  <si>
+    <t>Neuropsychiatric Lupus (NPSLE)</t>
+  </si>
+  <si>
+    <t>schema</t>
+  </si>
+  <si>
+    <t>CNS/PNS manifestations of SLE (seizure, psychosis, cognitive). Modeled as a phenotype subtype carrying a SeverityScore and organ-domain tag.</t>
+  </si>
+  <si>
+    <t>tissue-specific / cell-state-specific effects</t>
+  </si>
+  <si>
+    <t>cutaneous-lupus</t>
+  </si>
+  <si>
+    <t>Cutaneous Lupus</t>
+  </si>
+  <si>
+    <t>Skin-limited or skin-predominant lupus (acute/subacute/chronic discoid). Phenotype subtype with organ-domain = skin.</t>
+  </si>
+  <si>
+    <t>tissue-specific effects</t>
+  </si>
+  <si>
+    <t>organ-damage-slicc</t>
+  </si>
+  <si>
+    <t>Organ Damage (SLICC/ACR Damage Index)</t>
+  </si>
+  <si>
+    <t>Irreversible accumulated damage, SLICC-style. Modeled as a monotonic damage-accrual score distinct from reversible disease activity.</t>
+  </si>
+  <si>
+    <t>disease progression / feedback between progression and molecular state</t>
+  </si>
+  <si>
+    <t>seropositive-ra</t>
+  </si>
+  <si>
+    <t>Seropositive RA (ACPA/RF+)</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>RF/anti-CCP-positive RA; stronger HLA shared-epitope + PTPN22 association, more erosive. Phenotype subtype with a serostatus tag.</t>
+  </si>
+  <si>
+    <t>coding/HLA variants; ancestry-specific risk alleles</t>
+  </si>
+  <si>
+    <t>seronegative-ra</t>
+  </si>
+  <si>
+    <t>Seronegative RA (ACPA/RF-)</t>
+  </si>
+  <si>
+    <t>Autoantibody-negative RA; distinct genetic architecture and trajectory. Phenotype subtype.</t>
+  </si>
+  <si>
+    <t>heterogeneity within one disease</t>
+  </si>
+  <si>
+    <t>erosive-disease</t>
+  </si>
+  <si>
+    <t>Erosive Disease</t>
+  </si>
+  <si>
+    <t>Radiographic bone erosion; a structural-damage progression axis for RA, distinct from disease activity.</t>
+  </si>
+  <si>
+    <t>disease progression / organ damage</t>
+  </si>
+  <si>
+    <t>axial-psa</t>
+  </si>
+  <si>
+    <t>Axial Psoriatic Arthritis</t>
+  </si>
+  <si>
+    <t>PsA</t>
+  </si>
+  <si>
+    <t>Spinal/sacroiliac involvement of PsA. Phenotype subtype with axial domain tag.</t>
+  </si>
+  <si>
+    <t>enthesitis</t>
+  </si>
+  <si>
+    <t>Enthesitis</t>
+  </si>
+  <si>
+    <t>Inflammation at tendon/ligament insertions; hallmark of PsA/SpA. Phenotype subtype.</t>
+  </si>
+  <si>
+    <t>dactylitis</t>
+  </si>
+  <si>
+    <t>Dactylitis</t>
+  </si>
+  <si>
+    <t>'Sausage digit' — whole-digit swelling. PsA phenotype subtype.</t>
+  </si>
+  <si>
+    <t>uveitis</t>
+  </si>
+  <si>
+    <t>Uveitis</t>
+  </si>
+  <si>
+    <t>Inflammatory eye disease overlapping spondyloarthritis. Phenotype subtype / extra-articular domain.</t>
+  </si>
+  <si>
+    <t>pleiotropy / shared mechanism across tissues</t>
+  </si>
+  <si>
+    <t>ibd-overlap</t>
+  </si>
+  <si>
+    <t>Inflammatory Bowel Disease Overlap</t>
+  </si>
+  <si>
+    <t>Gut inflammation overlapping spondyloarthritis (IL-23/IL-17 axis shared). Phenotype subtype representing cross-disease pleiotropy.</t>
+  </si>
+  <si>
+    <t>pleiotropy / gene-environment-microbiome interaction</t>
+  </si>
+  <si>
+    <t>flare-pattern</t>
+  </si>
+  <si>
+    <t>Flare Pattern</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Episodic relapse of disease activity. v2 models flare-risk as a derived state on the progression machine, driven by serology trajectory.</t>
+  </si>
+  <si>
+    <t>feedback between disease progression and molecular state</t>
+  </si>
+  <si>
+    <t>disease-activity-score</t>
+  </si>
+  <si>
+    <t>Disease-Activity Score (SLEDAI / DAS28)</t>
+  </si>
+  <si>
+    <t>Composite activity indices (SLEDAI-2K for SLE, DAS28 for RA). v2 DERIVES an activity tier from raw component observations rather than hand-entering it.</t>
+  </si>
+  <si>
+    <t>calibrated severity / disease stage</t>
+  </si>
+  <si>
+    <t>treatment-line</t>
+  </si>
+  <si>
+    <t>Treatment Line</t>
+  </si>
+  <si>
+    <t>First-line / second-line / advanced-therapy sequencing. Modeled as an ordinal on therapies feeding treatment-line selection.</t>
+  </si>
+  <si>
+    <t>treatment histories / treatment-induced changes</t>
+  </si>
+  <si>
+    <t>adverse-event-surveillance</t>
+  </si>
+  <si>
+    <t>Adverse-Event Surveillance</t>
+  </si>
+  <si>
+    <t>vocabulary</t>
+  </si>
+  <si>
+    <t>Monitoring for therapy harms. Present as a concept/stressor type; the keystone already carries HasAdverseEffect at the leaf. Deep AE modeling is out-of-scope for the POC.</t>
+  </si>
+  <si>
+    <t>adverse effects</t>
+  </si>
+  <si>
+    <t>workflow-referral</t>
+  </si>
+  <si>
+    <t>Workflow: Referral</t>
+  </si>
+  <si>
+    <t>Entry into specialist care. Represented as the initial state of the clinical-workflow machine.</t>
+  </si>
+  <si>
+    <t>clinical workflow</t>
+  </si>
+  <si>
+    <t>workflow-differential</t>
+  </si>
+  <si>
+    <t>Workflow: Differential Diagnosis</t>
+  </si>
+  <si>
+    <t>Weighing competing diagnoses. Workflow state.</t>
+  </si>
+  <si>
+    <t>workflow-workup</t>
+  </si>
+  <si>
+    <t>Workflow: Workup</t>
+  </si>
+  <si>
+    <t>Ordering the labs/imaging that BECOME the raw leaves. Workflow state.</t>
+  </si>
+  <si>
+    <t>workflow-classification</t>
+  </si>
+  <si>
+    <t>Workflow: Classification</t>
+  </si>
+  <si>
+    <t>Applying classification criteria (e.g. EULAR/ACR). Workflow state.</t>
+  </si>
+  <si>
+    <t>workflow-baseline-severity</t>
+  </si>
+  <si>
+    <t>Workflow: Baseline Severity Assessment</t>
+  </si>
+  <si>
+    <t>Establishing baseline activity/damage. Workflow state; consumes the derived activity score.</t>
+  </si>
+  <si>
+    <t>clinical workflow / baseline severity</t>
+  </si>
+  <si>
+    <t>workflow-treatment-choice</t>
+  </si>
+  <si>
+    <t>Workflow: Treatment Choice</t>
+  </si>
+  <si>
+    <t>Selecting therapy; consumes the treatment-line-selection DAG. Workflow state.</t>
+  </si>
+  <si>
+    <t>clinical workflow / treatment</t>
+  </si>
+  <si>
+    <t>workflow-monitoring</t>
+  </si>
+  <si>
+    <t>Workflow: Monitoring</t>
+  </si>
+  <si>
+    <t>Longitudinal follow-up; produces the serology trajectory leaves. Workflow state.</t>
+  </si>
+  <si>
+    <t>clinical workflow / monitoring</t>
+  </si>
+  <si>
+    <t>workflow-flare-management</t>
+  </si>
+  <si>
+    <t>Workflow: Flare Management</t>
+  </si>
+  <si>
+    <t>Responding to a flare. Workflow state tied to the flare-risk progression state.</t>
+  </si>
+  <si>
+    <t>clinical workflow / flare</t>
+  </si>
+  <si>
+    <t>workflow-outcomes</t>
+  </si>
+  <si>
+    <t>Workflow: Long-Term Outcomes</t>
+  </si>
+  <si>
+    <t>Damage accrual, remission, outcomes over time. Workflow terminal state.</t>
+  </si>
+  <si>
+    <t>clinical workflow / outcomes</t>
   </si>
   <si>
     <t xml:space="preserve">{
@@ -18000,6 +18541,55 @@
         "Definition": "The skeptic's claim that a deterministic function over LLM-chosen inputs just launders a hallucination; defeated by externalized knobs + independent witness.",
         "Name": "laundering objection",
         "RelativePath": "/admin/glossary/gt-laundering-objection"
+      },
+      {
+        "GlossaryTermId": "gt-disease-state-simulator",
+        "Term": "disease state simulator",
+        "Definition": "The v2 layer the audit asked for: disease modeled as a WITNESSED state machine whose transitions fire only on raw longitudinal observations (rising anti-dsDNA, falling C3/C4, proteinuria). Current state and dwell-time are derived &amp; bitemporal — the contrast the audit drew with an 'evidence gate'.",
+        "Name": "disease state simulator",
+        "RelativePath": "/admin/glossary/gt-disease-state-simulator"
+      },
+      {
+        "GlossaryTermId": "gt-evidence-gate",
+        "Term": "evidence gate",
+        "Definition": "The v1 layer: per-patient adjudication of whether a prediction is trustworthy enough to act on (the four gates + IsClinicallyActionable). v2 keeps this and adds the disease-state simulator above it on the same hub.",
+        "Name": "evidence gate",
+        "RelativePath": "/admin/glossary/gt-evidence-gate"
+      },
+      {
+        "GlossaryTermId": "gt-disease-progression-machine",
+        "Term": "disease progression machine",
+        "Definition": "A state machine on the polymorphic StateMachines substrate whose subject is a patient's disease course (presymptomatic -&gt; serologic-active -&gt; early-nephritis -&gt; renal-flare-risk -&gt; biopsy-indicated). Transitions are raw-leaf-triggered; current state is the derived IsCurrent occupancy.",
+        "Name": "disease progression machine",
+        "RelativePath": "/admin/glossary/gt-disease-progression-machine"
+      },
+      {
+        "GlossaryTermId": "gt-dwell-time",
+        "Term": "dwell time",
+        "Definition": "Bitemporal derivation: how long a subject has been in a disease state (now - EnteredAt while current; ExitedAt - EnteredAt once left). The audit asked for 'how long has the patient/disease been in a state' — this is that, as a formula.",
+        "Name": "dwell time",
+        "RelativePath": "/admin/glossary/gt-dwell-time"
+      },
+      {
+        "GlossaryTermId": "gt-serology-trajectory",
+        "Term": "serology trajectory",
+        "Definition": "The raw longitudinal leaves driving progression: anti-dsDNA titre trend (rising/stable/falling), complement C3/C4 trend, proteinuria. The LLM/lab may emit these; everything above them is derived.",
+        "Name": "serology trajectory",
+        "RelativePath": "/admin/glossary/gt-serology-trajectory"
+      },
+      {
+        "GlossaryTermId": "gt-treatment-line-recommendation",
+        "Term": "treatment line recommendation",
+        "Definition": "Derived field: given the patient's confirmed causal mechanism + current disease state, the recommended therapy (MMF vs belimumab vs anifrolumab) and the single deciding reason. The audit's second worked example.",
+        "Name": "treatment line recommendation",
+        "RelativePath": "/admin/glossary/gt-treatment-line-recommendation"
+      },
+      {
+        "GlossaryTermId": "gt-corpus-discovery",
+        "Term": "corpus discovery",
+        "Definition": "The cohort-level surface where causal-hypothesis patterns EMERGE across many patients (vs v1's per-patient verdicts). Discovery is inherently corpus-level; this is the v2 reframe of the audit's 'you don't do discovery' critique.",
+        "Name": "corpus discovery",
+        "RelativePath": "/admin/glossary/gt-corpus-discovery"
       }
     ]
   },
@@ -18032,7 +18622,10 @@
         "datatype": "string",
         "type": "raw",
         "nullable": false,
-        "Description": "The one coherent rule-change / outcome."
+        "Description": "The one coherent rule-change / outco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">me."
       },
       {
         "name": "Status",
@@ -18129,10 +18722,7 @@
       {
         "LeopoldLoopId": "loop-0-5",
         "LoopNumber": "0.5",
-        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Title": "Test Harness First (the red contract)",
+        "Title": "Test Harness First (the red contract)",
         "Goal": "Ship a witnessed inference harness asserting the entire DAG x 7 patients via the app API; red on arrival, load-bearing.",
         "Status": "done",
         "RuleCommitMsg": "none - app-only loop, test-harness-first, no rule change",
@@ -18914,7 +19504,10 @@
         "IntakeClinicianCanCreate": null,
         "IntakeClinicianCanRead": null,
         "IntakeClinicianCanUpdate": null,
-        "IntakeClinicianCanDelete": null,
+        "IntakeClinicianCa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nDelete": null,
         "DiagnosingDoctorCanCreate": false,
         "DiagnosingDoctorCanRead": true,
         "DiagnosingDoctorCanUpdate": false,
@@ -19004,10 +19597,7 @@
         "AdminCanUpdate": true,
         "AdminCanDelete": true,
         "IntakeClinicianCanCreate": null,
-        "IntakeClini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cianCanRead": null,
+        "IntakeClinicianCanRead": null,
         "IntakeClinicianCanUpdate": null,
         "IntakeClinicianCanDelete": null,
         "DiagnosingDoctorCanCreate": false,
@@ -19819,7 +20409,10 @@
         "SubjectTableName": "IndividualPredictions",
         "SubjectStateColumn": "LifecycleStateKey",
         "CreatedBy": "build-seed",
-        "ModifiedBy": "build-seed",
+        "ModifiedBy"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: "build-seed",
         "Name": "diagnosis-lifecycle",
         "RelativePath": "/admin/state-machine/diagnosis-lifecycle",
         "MachineStates": null,
@@ -19932,10 +20525,7 @@
         "datatype": "datetime",
         "type": "raw",
         "nullable": true,
-        "Description": "Audit: when first inserted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">."
+        "Description": "Audit: when first inserted."
       },
       {
         "name": "CreatedBy",
@@ -20738,7 +21328,10 @@
         "StateMachine": "diagnosis-lifecycle",
         "SubjectTableName": "IndividualPredictions",
         "SubjectId": "pred-c",
-        "FromStateKey": "Intake",
+        "FromStateKey": "Intake",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
         "ToStateKey": "EvidenceAssessed",
         "TransitionAt": "2026-06-02T09:00:00Z",
         "TriggeredByRole": "system",
@@ -20820,10 +21413,7 @@
         "TriggeredByRole": "system",
         "Reason": "cryptic relatedness.",
         "CreatedBy": "build-seed",
-        "Mo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">difiedBy": "build-seed",
+        "ModifiedBy": "build-seed",
         "Name": "st-d-04-mechanismconfirmed-to-notactionable",
         "RelativePath": "/admin/state-machine/transitions/st-d-04-mechanismconfirmed-to-notactionable",
         "IsForward": true,
@@ -21588,7 +22178,10 @@
         "Name": "ssi-pred-d-notactionable-4",
         "RelativePath": "/admin/state-machine/instances/ssi-pred-d-notactionable-4",
         "IsCurrent": true,
-        "HasCompleteLineage": true,
+        "HasComp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leteLineage": true,
         "CreatedAt": null,
         "ModifiedAt": null,
         "ModifiedByModel": null
@@ -21678,10 +22271,7 @@
         "ModifiedByModel": null
       },
       {
-        "SubjectSta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teInstanceId": "ssi-pred-f-evidenceassessed-2",
+        "SubjectStateInstanceId": "ssi-pred-f-evidenceassessed-2",
         "StateMachine": "diagnosis-lifecycle",
         "SubjectTableName": "IndividualPredictions",
         "SubjectId": "pred-f",
@@ -22115,9 +22705,404 @@
       "export_mode": "rulebook_first",
       "vocabulary_coverage": "all domain terms in descriptions, field names, and data values"
     }
+  },
+  "DiseaseDomainConcepts": {
+    "Description": "v2 vocabulary completeness: every disease-domain concept the v1 audit named, with its modeling status and the challenge-stressor TYPE it instantiates. Makes the coverage claim checkable by grep, not by trust.",
+    "schema": [
+      {
+        "name": "DiseaseDomainConceptId",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": false,
+        "Description": "Slug PK."
+      },
+      {
+        "name": "ConceptLabel",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": false,
+        "Description": "Human-readable concept name (the audit's missing word)."
+      },
+      {
+        "name": "RelatedDisease",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": true,
+        "Description": "Disease this concept belongs to (SLE/RA/PsA/* for cross-cutting). Convention string, not a FK."
+      },
+      {
+        "name": "ModelingStatus",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": false,
+        "Description": "deep-dag | schema | vocabulary — how deeply v2 models this concept."
+      },
+      {
+        "name": "Definition",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": true,
+        "Description": "What the concept is and how v2 represents it."
+      },
+      {
+        "name": "ChallengeStressorType",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": true,
+        "Description": "Which TYPE of original-challenge stressor this concept instantiates (for the reconcile map)."
+      },
+      {
+        "name": "Name",
+        "datatype": "string",
+        "type": "calculated",
+        "nullable": true,
+        "Description": "Echoes ConceptLabel.",
+        "formula": "={{ConceptLabel}}"
+      },
+      {
+        "name": "RelativePath",
+        "datatype": "string",
+        "type": "calculated",
+        "nullable": true,
+        "Description": "Path to this concept's page.",
+        "formula": "=\"/admin/disease-concepts/\" &amp; {{DiseaseDomainConceptId}}"
+      },
+      {
+        "name": "IsDeeplyModeled",
+        "datatype": "boolean",
+        "type": "calculated",
+        "nullable": true,
+        "Description": "TRUE when this concept carries a witnessed inference DAG (status = deep-dag).",
+        "formula": "=IF({{ModelingStatus}}=\"deep-dag\", TRUE(), FALSE())"
+      },
+      {
+        "name": "IsSchemaModeled",
+        "datatype": "boolean",
+        "type": "calculated",
+        "nullable": true,
+        "Description": "TRUE when first-class schema/data (deep-dag or schema).",
+        "formula": "=IF(OR({{ModelingStatus}}=\"deep-dag\",{{ModelingStatus}}=\"schema\"), TRUE(), FALSE())"
+      }
+    ],
+    "data": [
+      {
+        "DiseaseDomainConceptId": "lupus-nephritis",
+        "ConceptLabel": "Lupus Nephritis",
+        "RelatedDisease": "SLE",
+        "ModelingStatus": "deep-dag",
+        "Definition": "Renal involvement of SLE; immune-complex glomerulonephritis. v2 models its PROGRESSION as a witnessed state machine driven by rising anti-dsDNA + falling complement + proteinuria.",
+        "ChallengeStressorType": "disease-progression / organ-specific subtype",
+        "Name": "Lupus Nephritis",
+        "RelativePath": "/admin/disease-concepts/lupus-nephritis",
+        "IsDeeplyModeled": true,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "treatment-line-selection",
+        "ConceptLabel": "Treatment-Line Selection",
+        "RelatedDisease": "SLE",
+        "ModelingStatus": "deep-dag",
+        "Definition": "Which therapy to choose given the patient's causal mechanism + disease state: mycophenolate (MMF) vs belimumab vs anifrolumab. v2 derives a recommended line + single deciding reason.",
+        "ChallengeStressorType": "treatment response / patient stratification",
+        "Name": "Treatment-Line Selection",
+        "RelativePath": "/admin/disease-concepts/treatment-line-selection",
+        "IsDeeplyModeled": true,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "neuropsychiatric-lupus",
+        "ConceptLabel": "Neuropsychiatric Lupus (NPSLE)",
+        "RelatedDisease": "SLE",
+        "ModelingStatus": "schema",
+        "Definition": "CNS/PNS manifestations of SLE (seizure, psychosis, cognitive). Modeled as a phenotype subtype carrying a SeverityScore and organ-domain tag.",
+        "ChallengeStressorType": "tissue-specific / cell-state-specific effects",
+        "Name": "Neuropsychiatric Lupus (NPSLE)",
+        "RelativePath": "/admin/disease-concepts/neuropsychiatric-lupus",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "cutaneous-lupus",
+        "ConceptLabel": "Cutaneous Lupus",
+        "RelatedDisease": "SLE",
+        "ModelingStatus": "schema",
+        "Definition": "Skin-limited or skin-predominant lupus (acute/subacute/chronic discoid). Phenotype subtype with organ-domain = skin.",
+        "ChallengeStressorType": "tissue-specific effects",
+        "Name": "Cutaneous Lupus",
+        "RelativePath": "/admin/disease-concepts/cutaneous-lupus",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "organ-damage-slicc",
+        "ConceptLabel": "Organ Damage (SLICC/ACR Damage Index)",
+        "RelatedDisease": "SLE",
+        "ModelingStatus": "schema",
+        "Definition": "Irreversible accumulated damage, SLICC-style. Modeled as a monotonic damage-accrual score distinct from reversible disease activity.",
+        "ChallengeStressorType": "disease progression / feedback between progression and molecular state",
+        "Name": "Organ Damage (SLICC/ACR Damage Index)",
+        "RelativePath": "/admin/disease-concepts/organ-damage-slicc",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "seropositive-ra",
+        "ConceptLabel": "Seropositive RA (ACPA/RF+)",
+        "RelatedDisease": "RA",
+        "ModelingStatus": "schema",
+        "Definition": "RF/anti-CCP-positive RA; stronger HLA shared-epitope + PTPN22 association, more erosive. Phenotype subtype with a serostatus tag.",
+        "ChallengeStressorType": "coding/HLA variants; ancestry-specific risk alleles",
+        "Name": "Seropositive RA (ACPA/RF+)",
+        "RelativePath": "/admin/disease-concepts/seropositive-ra",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "seronegative-ra",
+        "ConceptLabel": "Seronegative RA (ACPA/RF-)",
+        "RelatedDisease": "RA",
+        "ModelingStatus": "schema",
+        "Definition": "Autoantibody-negative RA; distinct genetic architecture and trajectory. Phenotype subtype.",
+        "ChallengeStressorType": "heterogeneity within one disease",
+        "Name": "Seronegative RA (ACPA/RF-)",
+        "RelativePath": "/admin/disease-concepts/seronegative-ra",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "erosive-disease",
+        "ConceptLabel": "Erosive Disease",
+        "RelatedDisease": "RA",
+        "ModelingStatus": "schema",
+        "Definition": "Radiographic bone erosion; a structural-damage progression axis for RA, distinct from disease activity.",
+        "ChallengeStressorType": "disease progression / organ damage",
+        "Name": "Erosive Disease",
+        "RelativePath": "/admin/disease-concepts/erosive-disease",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "axial-psa",
+        "ConceptLabel": "Axial Psoriatic Arthritis",
+        "RelatedDisease": "PsA",
+        "ModelingStatus": "schema",
+        "Definition": "Spinal/sacroiliac involvement of PsA. Phenotype subtype with axial domain tag.",
+        "ChallengeStressorType": "tissue-specific effects",
+        "Name": "Axial Psoriatic Arthritis",
+        "RelativePath": "/admin/disease-concepts/axial-psa",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "enthesitis",
+        "ConceptLabel": "Enthesitis",
+        "RelatedDisease": "PsA",
+        "ModelingStatus": "schema",
+        "Definition": "Inflammation at tendon/ligament insertions; hallmark of PsA/SpA. Phenotype subtype.",
+        "ChallengeStressorType": "tissue-specific effects",
+        "Name": "Enthesitis",
+        "RelativePath": "/admin/disease-concepts/enthesitis",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "dactylitis",
+        "ConceptLabel": "Dactylitis",
+        "RelatedDisease": "PsA",
+        "ModelingStatus": "schema",
+        "Definition": "'Sausage digit' — whole-digit swelling. PsA phenotype subtype.",
+        "ChallengeStressorType": "tissue-specific effects",
+        "Name": "Dactylitis",
+        "RelativePath": "/admin/disease-concepts/dactylitis",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "uveitis",
+        "ConceptLabel": "Uveitis",
+        "RelatedDisease": "PsA",
+        "ModelingStatus": "schema",
+        "Definition": "Inflammatory eye disease overlapping spondyloarthritis. Phenotype subtype / extra-articular domain.",
+        "ChallengeStressorType": "pleiotropy / shared mechanism across tissues",
+        "Name": "Uveitis",
+        "RelativePath": "/admin/disease-concepts/uveitis",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "ibd-overlap",
+        "ConceptLabel": "Inflammatory Bowel Disease Overlap",
+        "RelatedDisease": "PsA",
+        "ModelingStatus": "schema",
+        "Definition": "Gut inflammation overlapping spondyloarthritis (IL-23/IL-17 axis shared). Phenotype subtype representing cross-disease pleiotropy.",
+        "ChallengeStressorType": "pleiotropy / gene-environment-microbiome interaction",
+        "Name": "Inflammatory Bowel Disease Overlap",
+        "RelativePath": "/admin/disease-concepts/ibd-overlap",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "flare-pattern",
+        "ConceptLabel": </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Flare Pattern",
+        "RelatedDisease": "*",
+        "ModelingStatus": "schema",
+        "Definition": "Episodic relapse of disease activity. v2 models flare-risk as a derived state on the progression machine, driven by serology trajectory.",
+        "ChallengeStressorType": "feedback between disease progression and molecular state",
+        "Name": "Flare Pattern",
+        "RelativePath": "/admin/disease-concepts/flare-pattern",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "disease-activity-score",
+        "ConceptLabel": "Disease-Activity Score (SLEDAI / DAS28)",
+        "RelatedDisease": "*",
+        "ModelingStatus": "deep-dag",
+        "Definition": "Composite activity indices (SLEDAI-2K for SLE, DAS28 for RA). v2 DERIVES an activity tier from raw component observations rather than hand-entering it.",
+        "ChallengeStressorType": "calibrated severity / disease stage",
+        "Name": "Disease-Activity Score (SLEDAI / DAS28)",
+        "RelativePath": "/admin/disease-concepts/disease-activity-score",
+        "IsDeeplyModeled": true,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "treatment-line",
+        "ConceptLabel": "Treatment Line",
+        "RelatedDisease": "*",
+        "ModelingStatus": "schema",
+        "Definition": "First-line / second-line / advanced-therapy sequencing. Modeled as an ordinal on therapies feeding treatment-line selection.",
+        "ChallengeStressorType": "treatment histories / treatment-induced changes",
+        "Name": "Treatment Line",
+        "RelativePath": "/admin/disease-concepts/treatment-line",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": true
+      },
+      {
+        "DiseaseDomainConceptId": "adverse-event-surveillance",
+        "ConceptLabel": "Adverse-Event Surveillance",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Monitoring for therapy harms. Present as a concept/stressor type; the keystone already carries HasAdverseEffect at the leaf. Deep AE modeling is out-of-scope for the POC.",
+        "ChallengeStressorType": "adverse effects",
+        "Name": "Adverse-Event Surveillance",
+        "RelativePath": "/admin/disease-concepts/adverse-event-surveillance",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-referral",
+        "ConceptLabel": "Workflow: Referral",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Entry into specialist care. Represented as the initial state of the clinical-workflow machine.",
+        "ChallengeStressorType": "clinical workflow",
+        "Name": "Workflow: Referral",
+        "RelativePath": "/admin/disease-concepts/workflow-referral",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-differential",
+        "ConceptLabel": "Workflow: Differential Diagnosis",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Weighing competing diagnoses. Workflow state.",
+        "ChallengeStressorType": "clinical workflow",
+        "Name": "Workflow: Differential Diagnosis",
+        "RelativePath": "/admin/disease-concepts/workflow-differential",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-workup",
+        "ConceptLabel": "Workflow: Workup",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Ordering the labs/imaging that BECOME the raw leaves. Workflow state.",
+        "ChallengeStressorType": "clinical workflow",
+        "Name": "Workflow: Workup",
+        "RelativePath": "/admin/disease-concepts/workflow-workup",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-classification",
+        "ConceptLabel": "Workflow: Classification",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Applying classification criteria (e.g. EULAR/ACR). Workflow state.",
+        "ChallengeStressorType": "clinical workflow",
+        "Name": "Workflow: Classification",
+        "RelativePath": "/admin/disease-concepts/workflow-classification",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-baseline-severity",
+        "ConceptLabel": "Workflow: Baseline Severity Assessment",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Establishing baseline activity/damage. Workflow state; consumes the derived activity score.",
+        "ChallengeStressorType": "clinical workflow / baseline severity",
+        "Name": "Workflow: Baseline Severity Assessment",
+        "RelativePath": "/admin/disease-concepts/workflow-baseline-severity",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-treatment-choice",
+        "ConceptLabel": "Workflow: Treatment Choice",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Selecting therapy; consumes the treatment-line-selection DAG. Workflow state.",
+        "ChallengeStressorType": "clinical workflow / treatment",
+        "Name": "Workflow: Treatment Choice",
+        "RelativePath": "/admin/disease-concepts/workflow-treatment-choice",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-monitoring",
+        "ConceptLabel": "Workflow: Monitoring",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Longitudinal follow-up; produces the serology trajectory leaves. Workflow state.",
+        "ChallengeStressorType": "clinical workflow / monitoring",
+        "Name": "Workflow: Monitoring",
+        "RelativePath": "/admin/disease-concepts/workflow-monitoring",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-flare-management",
+        "ConceptLabel": "Workflow: Flare Management",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Responding to a flare. Workflow state tied to the flare-risk progression state.",
+        "ChallengeStressorType": "clinical workflow / flare",
+        "Name": "Workflow: Flare Management",
+        "RelativePath": "/admin/disease-concepts/workflow-flare-management",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      },
+      {
+        "DiseaseDomainConceptId": "workflow-outcomes",
+        "ConceptLabel": "Workflow: Long-Term Outcomes",
+        "RelatedDisease": "*",
+        "ModelingStatus": "vocabulary",
+        "Definition": "Damage accrual, remission, outcomes over time. Workflow terminal state.",
+        "ChallengeStressorType": "clinical workflow / outcomes",
+        "Name": "Workflow: Long-Term Outcomes",
+        "RelativePath": "/admin/disease-concepts/workflow-outcomes",
+        "IsDeeplyModeled": false,
+        "IsSchemaModeled": false
+      }
+    ]
   }
-}
-</t>
+}</t>
   </si>
 </sst>
 </file>
@@ -32642,14 +33627,14 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.16391944885254" customWidth="1"/>
-    <col min="2" max="2" width="20.549789428710938" customWidth="1"/>
-    <col min="3" max="3" width="150.76243591308594" customWidth="1"/>
-    <col min="4" max="4" width="20.549789428710938" customWidth="1"/>
-    <col min="5" max="5" width="38.48448944091797" customWidth="1"/>
+    <col min="1" max="1" width="33.37306594848633" customWidth="1"/>
+    <col min="2" max="2" width="30.477060317993164" customWidth="1"/>
+    <col min="3" max="3" width="256" customWidth="1"/>
+    <col min="4" max="4" width="30.477060317993164" customWidth="1"/>
+    <col min="5" max="5" width="49.50783920288086" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32781,6 +33766,139 @@
       <c r="E7" s="3" t="str">
         <f>"/admin/glossary/" &amp; A7</f>
         <v>/admin/glossary/gt-laundering-objection</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D8" s="3" t="str">
+        <f>B8</f>
+        <v>disease state simulator</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A8</f>
+        <v>/admin/glossary/gt-disease-state-simulator</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="D9" s="3" t="str">
+        <f>B9</f>
+        <v>evidence gate</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A9</f>
+        <v>/admin/glossary/gt-evidence-gate</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="D10" s="3" t="str">
+        <f>B10</f>
+        <v>disease progression machine</v>
+      </c>
+      <c r="E10" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A10</f>
+        <v>/admin/glossary/gt-disease-progression-machine</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="D11" s="3" t="str">
+        <f>B11</f>
+        <v>dwell time</v>
+      </c>
+      <c r="E11" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A11</f>
+        <v>/admin/glossary/gt-dwell-time</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>B12</f>
+        <v>serology trajectory</v>
+      </c>
+      <c r="E12" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A12</f>
+        <v>/admin/glossary/gt-serology-trajectory</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f>B13</f>
+        <v>treatment line recommendation</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A13</f>
+        <v>/admin/glossary/gt-treatment-line-recommendation</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D14" s="3" t="str">
+        <f>B14</f>
+        <v>corpus discovery</v>
+      </c>
+      <c r="E14" s="3" t="str">
+        <f>"/admin/glossary/" &amp; A14</f>
+        <v>/admin/glossary/gt-corpus-discovery</v>
       </c>
     </row>
   </sheetData>
@@ -32813,25 +33931,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>777</v>
+        <v>798</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>778</v>
+        <v>799</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>687</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>646</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>781</v>
+        <v>802</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -32843,39 +33961,39 @@
         <v>4</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>782</v>
+        <v>803</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>783</v>
+        <v>804</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>784</v>
+        <v>805</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>785</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>786</v>
+        <v>807</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>787</v>
+        <v>808</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>789</v>
+        <v>810</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="H2" s="2">
         <v>0</v>
@@ -32897,33 +34015,33 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>794</v>
+        <v>815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>800</v>
+        <v>821</v>
       </c>
       <c r="H3" s="2">
         <v>1</v>
@@ -32945,33 +34063,33 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>801</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>802</v>
+        <v>823</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>804</v>
+        <v>825</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>805</v>
+        <v>826</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>806</v>
+        <v>827</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>807</v>
+        <v>828</v>
       </c>
       <c r="H4" s="2">
         <v>2</v>
@@ -32993,7 +34111,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>202</v>
@@ -33004,22 +34122,22 @@
         <v>702</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>808</v>
+        <v>829</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>809</v>
+        <v>830</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>810</v>
+        <v>831</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>811</v>
+        <v>832</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
@@ -33041,7 +34159,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>202</v>
@@ -33052,22 +34170,22 @@
         <v>706</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>813</v>
+        <v>834</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>814</v>
+        <v>835</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>815</v>
+        <v>836</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="H6" s="2">
         <v>4</v>
@@ -33089,7 +34207,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>202</v>
@@ -33097,25 +34215,25 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>818</v>
+        <v>839</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>819</v>
+        <v>840</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>820</v>
+        <v>841</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>821</v>
+        <v>842</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>822</v>
+        <v>843</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>823</v>
+        <v>844</v>
       </c>
       <c r="H7" s="2">
         <v>5</v>
@@ -33137,7 +34255,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>202</v>
@@ -33145,25 +34263,25 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>827</v>
+        <v>848</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>829</v>
+        <v>850</v>
       </c>
       <c r="H8" s="2">
         <v>6</v>
@@ -33185,7 +34303,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>793</v>
+        <v>814</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>202</v>
@@ -33193,25 +34311,25 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>830</v>
+        <v>851</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>831</v>
+        <v>852</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>832</v>
+        <v>853</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>834</v>
+        <v>855</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>835</v>
+        <v>856</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>836</v>
+        <v>857</v>
       </c>
       <c r="H9" s="2">
         <v>7</v>
@@ -33233,7 +34351,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>202</v>
@@ -33241,19 +34359,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>839</v>
+        <v>860</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>202</v>
@@ -33281,7 +34399,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>202</v>
@@ -33289,19 +34407,19 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>842</v>
+        <v>863</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>202</v>
@@ -33329,7 +34447,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>843</v>
+        <v>864</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>202</v>
@@ -33395,16 +34513,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>688</v>
@@ -33413,136 +34531,136 @@
         <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>858</v>
+        <v>879</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>872</v>
+        <v>893</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C2), " ", "-")</f>
         <v>intake</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="F2" s="2">
         <v>10</v>
@@ -33551,22 +34669,22 @@
         <v>202</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="N2" s="2" t="b">
         <v>0</v>
@@ -33575,10 +34693,10 @@
         <v>1</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>202</v>
@@ -33668,54 +34786,54 @@
       </c>
       <c r="AN2" s="6"/>
       <c r="AO2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C3), " ", "-")</f>
         <v>new-patient</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
       <c r="F3" s="2">
         <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="N3" s="2" t="b">
         <v>1</v>
@@ -33724,10 +34842,10 @@
         <v>0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>202</v>
@@ -33817,54 +34935,54 @@
       </c>
       <c r="AN3" s="6"/>
       <c r="AO3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C4), " ", "-")</f>
         <v>observations</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="F4" s="2">
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="N4" s="2" t="b">
         <v>1</v>
@@ -33873,10 +34991,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>202</v>
@@ -33966,54 +35084,54 @@
       </c>
       <c r="AN4" s="6"/>
       <c r="AO4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP4" s="6"/>
       <c r="AQ4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C5), " ", "-")</f>
         <v>variants</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>917</v>
+        <v>938</v>
       </c>
       <c r="F5" s="2">
         <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>918</v>
+        <v>939</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>91</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
       <c r="N5" s="2" t="b">
         <v>1</v>
@@ -34022,10 +35140,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>202</v>
@@ -34115,54 +35233,54 @@
       </c>
       <c r="AN5" s="6"/>
       <c r="AO5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C6), " ", "-")</f>
         <v>assays</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
       <c r="F6" s="2">
         <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>926</v>
+        <v>947</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>927</v>
+        <v>948</v>
       </c>
       <c r="N6" s="2" t="b">
         <v>1</v>
@@ -34171,10 +35289,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>202</v>
@@ -34264,50 +35382,50 @@
       </c>
       <c r="AN6" s="6"/>
       <c r="AO6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP6" s="6"/>
       <c r="AQ6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C7), " ", "-")</f>
         <v>submit-case</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="F7" s="2">
         <v>15</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="N7" s="2" t="b">
         <v>1</v>
@@ -34316,10 +35434,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>202</v>
@@ -34409,30 +35527,30 @@
       </c>
       <c r="AN7" s="6"/>
       <c r="AO7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP7" s="6"/>
       <c r="AQ7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C8), " ", "-")</f>
         <v>diagnosis</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="F8" s="2">
         <v>20</v>
@@ -34441,22 +35559,22 @@
         <v>202</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
       <c r="N8" s="2" t="b">
         <v>0</v>
@@ -34465,13 +35583,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S8" s="2" t="s">
         <v>202</v>
@@ -34558,54 +35676,54 @@
       </c>
       <c r="AN8" s="6"/>
       <c r="AO8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP8" s="6"/>
       <c r="AQ8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C9), " ", "-")</f>
         <v>case</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
       <c r="F9" s="2">
         <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
       <c r="N9" s="2" t="b">
         <v>1</v>
@@ -34614,13 +35732,13 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S9" s="2" t="s">
         <v>202</v>
@@ -34707,54 +35825,54 @@
       </c>
       <c r="AN9" s="6"/>
       <c r="AO9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP9" s="6"/>
       <c r="AQ9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C10), " ", "-")</f>
         <v>evidence</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>953</v>
+        <v>974</v>
       </c>
       <c r="F10" s="2">
         <v>22</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>200</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="N10" s="2" t="b">
         <v>1</v>
@@ -34763,13 +35881,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S10" s="2" t="s">
         <v>202</v>
@@ -34856,54 +35974,54 @@
       </c>
       <c r="AN10" s="6"/>
       <c r="AO10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP10" s="6"/>
       <c r="AQ10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C11), " ", "-")</f>
         <v>mechanism</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="F11" s="2">
         <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>961</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>940</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
       <c r="N11" s="2" t="b">
         <v>1</v>
@@ -34912,13 +36030,13 @@
         <v>0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>202</v>
@@ -35005,54 +36123,54 @@
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP11" s="6"/>
       <c r="AQ11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="B12" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C12), " ", "-")</f>
         <v>replication</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>967</v>
+        <v>988</v>
       </c>
       <c r="F12" s="2">
         <v>24</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>968</v>
+        <v>989</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>74</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
       <c r="N12" s="2" t="b">
         <v>1</v>
@@ -35061,13 +36179,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>202</v>
@@ -35154,54 +36272,54 @@
       </c>
       <c r="AN12" s="6"/>
       <c r="AO12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP12" s="6"/>
       <c r="AQ12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="B13" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C13), " ", "-")</f>
         <v>neg-controls</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="F13" s="2">
         <v>25</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>975</v>
+        <v>996</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>456</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>976</v>
+        <v>997</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="N13" s="2" t="b">
         <v>1</v>
@@ -35210,13 +36328,13 @@
         <v>0</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S13" s="2" t="s">
         <v>202</v>
@@ -35303,54 +36421,54 @@
       </c>
       <c r="AN13" s="6"/>
       <c r="AO13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C14), " ", "-")</f>
         <v>calibration</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>979</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>981</v>
+        <v>1002</v>
       </c>
       <c r="F14" s="2">
         <v>26</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>982</v>
+        <v>1003</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>512</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>983</v>
+        <v>1004</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
       <c r="N14" s="2" t="b">
         <v>1</v>
@@ -35359,13 +36477,13 @@
         <v>0</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>202</v>
@@ -35452,54 +36570,54 @@
       </c>
       <c r="AN14" s="6"/>
       <c r="AO14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP14" s="6"/>
       <c r="AQ14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C15), " ", "-")</f>
         <v>gates</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="F15" s="2">
         <v>27</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>990</v>
+        <v>1011</v>
       </c>
       <c r="N15" s="2" t="b">
         <v>1</v>
@@ -35508,13 +36626,13 @@
         <v>0</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>202</v>
@@ -35601,54 +36719,54 @@
       </c>
       <c r="AN15" s="6"/>
       <c r="AO15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP15" s="6"/>
       <c r="AQ15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C16), " ", "-")</f>
         <v>keystone</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>993</v>
+        <v>1014</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="F16" s="2">
         <v>28</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="N16" s="2" t="b">
         <v>1</v>
@@ -35657,13 +36775,13 @@
         <v>0</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>202</v>
@@ -35750,54 +36868,54 @@
       </c>
       <c r="AN16" s="6"/>
       <c r="AO16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP16" s="6"/>
       <c r="AQ16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="B17" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C17), " ", "-")</f>
         <v>report</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="F17" s="2">
         <v>29</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1001</v>
+        <v>1022</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>1002</v>
+        <v>1023</v>
       </c>
       <c r="N17" s="2" t="b">
         <v>1</v>
@@ -35806,13 +36924,13 @@
         <v>0</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>202</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>202</v>
@@ -35899,30 +37017,30 @@
       </c>
       <c r="AN17" s="6"/>
       <c r="AO17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP17" s="6"/>
       <c r="AQ17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="B18" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C18), " ", "-")</f>
         <v>admin</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1006</v>
+        <v>1027</v>
       </c>
       <c r="F18" s="2">
         <v>90</v>
@@ -35931,18 +37049,18 @@
         <v>202</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="s">
-        <v>1008</v>
+        <v>1029</v>
       </c>
       <c r="N18" s="2" t="b">
         <v>0</v>
@@ -35951,7 +37069,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>202</v>
@@ -36044,50 +37162,50 @@
       </c>
       <c r="AN18" s="6"/>
       <c r="AO18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP18" s="6"/>
       <c r="AQ18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1009</v>
+        <v>1030</v>
       </c>
       <c r="B19" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C19), " ", "-")</f>
         <v>harness</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1011</v>
+        <v>1032</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1012</v>
+        <v>1033</v>
       </c>
       <c r="F19" s="2">
         <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1013</v>
+        <v>1034</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2" t="s">
-        <v>1014</v>
+        <v>1035</v>
       </c>
       <c r="N19" s="2" t="b">
         <v>0</v>
@@ -36096,7 +37214,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>202</v>
@@ -36189,54 +37307,54 @@
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP19" s="6"/>
       <c r="AQ19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1015</v>
+        <v>1036</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C20), " ", "-")</f>
         <v>routing</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1016</v>
+        <v>1037</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1017</v>
+        <v>1038</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="F20" s="2">
         <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1019</v>
+        <v>1040</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1021</v>
+        <v>1042</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="N20" s="2" t="b">
         <v>0</v>
@@ -36245,7 +37363,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>202</v>
@@ -36338,54 +37456,54 @@
       </c>
       <c r="AN20" s="6"/>
       <c r="AO20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP20" s="6"/>
       <c r="AQ20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1023</v>
+        <v>1044</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C21), " ", "-")</f>
         <v>state-machine</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1024</v>
+        <v>1045</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1025</v>
+        <v>1046</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1026</v>
+        <v>1047</v>
       </c>
       <c r="F21" s="2">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1027</v>
+        <v>1048</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1028</v>
+        <v>1049</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1029</v>
+        <v>1050</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>1030</v>
+        <v>1051</v>
       </c>
       <c r="N21" s="2" t="b">
         <v>0</v>
@@ -36394,7 +37512,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>202</v>
@@ -36487,50 +37605,50 @@
       </c>
       <c r="AN21" s="6"/>
       <c r="AO21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1031</v>
+        <v>1052</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C22), " ", "-")</f>
         <v>explainer-dag</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1032</v>
+        <v>1053</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1033</v>
+        <v>1054</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1034</v>
+        <v>1055</v>
       </c>
       <c r="F22" s="2">
         <v>94</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1035</v>
+        <v>1056</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2" t="s">
-        <v>1036</v>
+        <v>1057</v>
       </c>
       <c r="N22" s="2" t="b">
         <v>0</v>
@@ -36539,7 +37657,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>202</v>
@@ -36632,54 +37750,54 @@
       </c>
       <c r="AN22" s="6"/>
       <c r="AO22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP22" s="6"/>
       <c r="AQ22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C23), " ", "-")</f>
         <v>cohort</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1038</v>
+        <v>1059</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1039</v>
+        <v>1060</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1040</v>
+        <v>1061</v>
       </c>
       <c r="F23" s="2">
         <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>1042</v>
+        <v>1063</v>
       </c>
       <c r="N23" s="2" t="b">
         <v>0</v>
@@ -36688,7 +37806,7 @@
         <v>0</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q23" s="2" t="s">
         <v>202</v>
@@ -36781,54 +37899,54 @@
       </c>
       <c r="AN23" s="6"/>
       <c r="AO23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP23" s="6"/>
       <c r="AQ23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1043</v>
+        <v>1064</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C24), " ", "-")</f>
         <v>leopold-loops</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1044</v>
+        <v>1065</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1045</v>
+        <v>1066</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="F24" s="2">
         <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1047</v>
+        <v>1068</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1049</v>
+        <v>1070</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1050</v>
+        <v>1071</v>
       </c>
       <c r="N24" s="2" t="b">
         <v>0</v>
@@ -36837,7 +37955,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="Q24" s="2" t="s">
         <v>202</v>
@@ -36930,11 +38048,11 @@
       </c>
       <c r="AN24" s="6"/>
       <c r="AO24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AP24" s="6"/>
       <c r="AQ24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="AR24" s="2"/>
     </row>
@@ -37116,7 +38234,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1051</v>
+        <v>1072</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -37131,45 +38249,45 @@
         <v>688</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1053</v>
+        <v>1074</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1056</v>
+        <v>1077</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1057</v>
+        <v>1078</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1058</v>
+        <v>1079</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>A2</f>
@@ -37180,10 +38298,10 @@
         <v>/admin/state-machine/diagnosis-lifecycle</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1061</v>
+        <v>1082</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>10</v>
@@ -37204,11 +38322,11 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q2" s="2"/>
     </row>
@@ -37244,7 +38362,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1062</v>
+        <v>1083</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -37253,48 +38371,48 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>687</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1068</v>
+        <v>1089</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1069</v>
+        <v>1090</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1070</v>
+        <v>1091</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>A2</f>
@@ -37305,13 +38423,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--intake</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -37326,17 +38444,17 @@
       <c r="K2" s="2"/>
       <c r="L2" s="6"/>
       <c r="M2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>A3</f>
@@ -37347,13 +38465,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--evidenceassessed</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="G3" s="2">
         <v>2</v>
@@ -37368,17 +38486,17 @@
       <c r="K3" s="2"/>
       <c r="L3" s="6"/>
       <c r="M3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>A4</f>
@@ -37389,13 +38507,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--mechanismconfirmed</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="G4" s="2">
         <v>3</v>
@@ -37410,17 +38528,17 @@
       <c r="K4" s="2"/>
       <c r="L4" s="6"/>
       <c r="M4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>A5</f>
@@ -37431,13 +38549,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--calibrationchecked</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="G5" s="2">
         <v>4</v>
@@ -37452,17 +38570,17 @@
       <c r="K5" s="2"/>
       <c r="L5" s="6"/>
       <c r="M5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>A6</f>
@@ -37473,13 +38591,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--transportchecked</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -37494,17 +38612,17 @@
       <c r="K6" s="2"/>
       <c r="L6" s="6"/>
       <c r="M6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>A7</f>
@@ -37515,13 +38633,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--actionable</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="G7" s="2">
         <v>6</v>
@@ -37536,17 +38654,17 @@
       <c r="K7" s="2"/>
       <c r="L7" s="6"/>
       <c r="M7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>A8</f>
@@ -37557,13 +38675,13 @@
         <v>/admin/state-machine/states/diagnosis-lifecycle--notactionable</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="G8" s="2">
         <v>7</v>
@@ -37578,11 +38696,11 @@
       <c r="K8" s="2"/>
       <c r="L8" s="6"/>
       <c r="M8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P8" s="2"/>
     </row>
@@ -37620,7 +38738,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1083</v>
+        <v>1104</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -37629,54 +38747,54 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1084</v>
+        <v>1105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1086</v>
+        <v>1107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1093</v>
+        <v>1114</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>A2</f>
@@ -37687,21 +38805,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--intake-&gt;evidenceassessed</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1070</v>
+        <v>1091</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K2" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E2,MachineStates!A2:A999, 0))</f>
@@ -37717,17 +38835,17 @@
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1096</v>
+        <v>1117</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>A3</f>
@@ -37738,21 +38856,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--evidenceassessed-&gt;mechanismconfirmed</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1097</v>
+        <v>1118</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K3" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E3,MachineStates!A2:A999, 0))</f>
@@ -37768,17 +38886,17 @@
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P3" s="6"/>
       <c r="Q3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1098</v>
+        <v>1119</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>A4</f>
@@ -37789,21 +38907,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--evidenceassessed-&gt;notactionable</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1099</v>
+        <v>1120</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K4" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E4,MachineStates!A2:A999, 0))</f>
@@ -37819,17 +38937,17 @@
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>A5</f>
@@ -37840,21 +38958,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--mechanismconfirmed-&gt;calibrationchecked</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K5" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E5,MachineStates!A2:A999, 0))</f>
@@ -37870,17 +38988,17 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1102</v>
+        <v>1123</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>A6</f>
@@ -37891,21 +39009,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--mechanismconfirmed-&gt;notactionable</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1103</v>
+        <v>1124</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K6" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E6,MachineStates!A2:A999, 0))</f>
@@ -37921,17 +39039,17 @@
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>A7</f>
@@ -37942,21 +39060,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--calibrationchecked-&gt;transportchecked</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1105</v>
+        <v>1126</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K7" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E7,MachineStates!A2:A999, 0))</f>
@@ -37972,17 +39090,17 @@
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1106</v>
+        <v>1127</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>A8</f>
@@ -37993,21 +39111,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--calibrationchecked-&gt;notactionable</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1107</v>
+        <v>1128</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K8" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E8,MachineStates!A2:A999, 0))</f>
@@ -38023,17 +39141,17 @@
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1108</v>
+        <v>1129</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>A9</f>
@@ -38044,21 +39162,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--transportchecked-&gt;actionable</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1109</v>
+        <v>1130</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K9" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E9,MachineStates!A2:A999, 0))</f>
@@ -38074,17 +39192,17 @@
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1110</v>
+        <v>1131</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>A10</f>
@@ -38095,21 +39213,21 @@
         <v>/admin/state-machine/rules/diagnosis-lifecycle--transportchecked-&gt;notactionable</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1111</v>
+        <v>1132</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K10" s="3" t="str">
         <f>INDEX(MachineStates!E2:E999, MATCH(E10,MachineStates!A2:A999, 0))</f>
@@ -38125,11 +39243,11 @@
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="R10" s="2"/>
     </row>
@@ -38166,7 +39284,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1112</v>
+        <v>1133</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -38175,51 +39293,51 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1113</v>
+        <v>1134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1114</v>
+        <v>1135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1115</v>
+        <v>1136</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>A2</f>
@@ -38230,7 +39348,7 @@
         <v>/admin/state-machine/transitions/st-a-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -38239,19 +39357,19 @@
         <v>513</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I2" s="2">
         <v>46175.375</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L2" s="3" t="b">
         <f>NOT(H2="Intake")</f>
@@ -38259,17 +39377,17 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1119</v>
+        <v>1140</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>A3</f>
@@ -38280,7 +39398,7 @@
         <v>/admin/state-machine/transitions/st-a-03-evidenceassessed-to-mechanismconfirmed</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -38289,19 +39407,19 @@
         <v>513</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="I3" s="2">
         <v>46176.375</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="L3" s="3" t="b">
         <f>NOT(H3="Intake")</f>
@@ -38309,17 +39427,17 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>A4</f>
@@ -38330,7 +39448,7 @@
         <v>/admin/state-machine/transitions/st-a-04-mechanismconfirmed-to-calibrationchecked</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
@@ -38339,19 +39457,19 @@
         <v>513</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="I4" s="2">
         <v>46177.375</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="L4" s="3" t="b">
         <f>NOT(H4="Intake")</f>
@@ -38359,17 +39477,17 @@
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>A5</f>
@@ -38380,7 +39498,7 @@
         <v>/admin/state-machine/transitions/st-a-05-calibrationchecked-to-transportchecked</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
@@ -38389,19 +39507,19 @@
         <v>513</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="I5" s="2">
         <v>46178.375</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="L5" s="3" t="b">
         <f>NOT(H5="Intake")</f>
@@ -38409,17 +39527,17 @@
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>A6</f>
@@ -38430,7 +39548,7 @@
         <v>/admin/state-machine/transitions/st-a-06-transportchecked-to-actionable</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -38439,19 +39557,19 @@
         <v>513</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="I6" s="2">
         <v>46179.375</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1126</v>
+        <v>1147</v>
       </c>
       <c r="L6" s="3" t="b">
         <f>NOT(H6="Intake")</f>
@@ -38459,17 +39577,17 @@
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1127</v>
+        <v>1148</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>A7</f>
@@ -38480,7 +39598,7 @@
         <v>/admin/state-machine/transitions/st-b-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
@@ -38489,19 +39607,19 @@
         <v>515</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I7" s="2">
         <v>46175.375</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L7" s="3" t="b">
         <f>NOT(H7="Intake")</f>
@@ -38509,17 +39627,17 @@
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1128</v>
+        <v>1149</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>A8</f>
@@ -38530,7 +39648,7 @@
         <v>/admin/state-machine/transitions/st-b-03-evidenceassessed-to-mechanismconfirmed</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
@@ -38539,19 +39657,19 @@
         <v>515</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="I8" s="2">
         <v>46176.375</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="L8" s="3" t="b">
         <f>NOT(H8="Intake")</f>
@@ -38559,17 +39677,17 @@
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>A9</f>
@@ -38580,7 +39698,7 @@
         <v>/admin/state-machine/transitions/st-b-04-mechanismconfirmed-to-calibrationchecked</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
@@ -38589,19 +39707,19 @@
         <v>515</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="I9" s="2">
         <v>46177.375</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="L9" s="3" t="b">
         <f>NOT(H9="Intake")</f>
@@ -38609,17 +39727,17 @@
       </c>
       <c r="M9" s="6"/>
       <c r="N9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1130</v>
+        <v>1151</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>A10</f>
@@ -38630,7 +39748,7 @@
         <v>/admin/state-machine/transitions/st-b-05-calibrationchecked-to-notactionable</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -38639,19 +39757,19 @@
         <v>515</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="I10" s="2">
         <v>46178.375</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1131</v>
+        <v>1152</v>
       </c>
       <c r="L10" s="3" t="b">
         <f>NOT(H10="Intake")</f>
@@ -38659,17 +39777,17 @@
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1132</v>
+        <v>1153</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>A11</f>
@@ -38680,7 +39798,7 @@
         <v>/admin/state-machine/transitions/st-c-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
@@ -38689,19 +39807,19 @@
         <v>516</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I11" s="2">
         <v>46175.375</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L11" s="3" t="b">
         <f>NOT(H11="Intake")</f>
@@ -38709,17 +39827,17 @@
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1133</v>
+        <v>1154</v>
       </c>
       <c r="B12" s="3" t="str">
         <f>A12</f>
@@ -38730,7 +39848,7 @@
         <v>/admin/state-machine/transitions/st-c-03-evidenceassessed-to-notactionable</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -38739,19 +39857,19 @@
         <v>516</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="I12" s="2">
         <v>46176.375</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1134</v>
+        <v>1155</v>
       </c>
       <c r="L12" s="3" t="b">
         <f>NOT(H12="Intake")</f>
@@ -38759,17 +39877,17 @@
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="3" t="str">
         <f>A13</f>
@@ -38780,7 +39898,7 @@
         <v>/admin/state-machine/transitions/st-d-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
@@ -38789,19 +39907,19 @@
         <v>517</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I13" s="2">
         <v>46175.375</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L13" s="3" t="b">
         <f>NOT(H13="Intake")</f>
@@ -38809,17 +39927,17 @@
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>1136</v>
+        <v>1157</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>A14</f>
@@ -38830,7 +39948,7 @@
         <v>/admin/state-machine/transitions/st-d-03-evidenceassessed-to-mechanismconfirmed</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -38839,19 +39957,19 @@
         <v>517</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="I14" s="2">
         <v>46176.375</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="L14" s="3" t="b">
         <f>NOT(H14="Intake")</f>
@@ -38859,17 +39977,17 @@
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1137</v>
+        <v>1158</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>A15</f>
@@ -38880,7 +39998,7 @@
         <v>/admin/state-machine/transitions/st-d-04-mechanismconfirmed-to-notactionable</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -38889,19 +40007,19 @@
         <v>517</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="I15" s="2">
         <v>46177.375</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1138</v>
+        <v>1159</v>
       </c>
       <c r="L15" s="3" t="b">
         <f>NOT(H15="Intake")</f>
@@ -38909,17 +40027,17 @@
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1139</v>
+        <v>1160</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>A16</f>
@@ -38930,7 +40048,7 @@
         <v>/admin/state-machine/transitions/st-e-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -38939,19 +40057,19 @@
         <v>518</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I16" s="2">
         <v>46175.375</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L16" s="3" t="b">
         <f>NOT(H16="Intake")</f>
@@ -38959,17 +40077,17 @@
       </c>
       <c r="M16" s="6"/>
       <c r="N16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1140</v>
+        <v>1161</v>
       </c>
       <c r="B17" s="3" t="str">
         <f>A17</f>
@@ -38980,7 +40098,7 @@
         <v>/admin/state-machine/transitions/st-e-03-evidenceassessed-to-notactionable</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
@@ -38989,19 +40107,19 @@
         <v>518</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="I17" s="2">
         <v>46176.375</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1141</v>
+        <v>1162</v>
       </c>
       <c r="L17" s="3" t="b">
         <f>NOT(H17="Intake")</f>
@@ -39009,17 +40127,17 @@
       </c>
       <c r="M17" s="6"/>
       <c r="N17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1142</v>
+        <v>1163</v>
       </c>
       <c r="B18" s="3" t="str">
         <f>A18</f>
@@ -39030,7 +40148,7 @@
         <v>/admin/state-machine/transitions/st-f-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
@@ -39039,19 +40157,19 @@
         <v>519</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I18" s="2">
         <v>46175.375</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L18" s="3" t="b">
         <f>NOT(H18="Intake")</f>
@@ -39059,17 +40177,17 @@
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="B19" s="3" t="str">
         <f>A19</f>
@@ -39080,7 +40198,7 @@
         <v>/admin/state-machine/transitions/st-f-03-evidenceassessed-to-mechanismconfirmed</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
@@ -39089,19 +40207,19 @@
         <v>519</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="I19" s="2">
         <v>46176.375</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="L19" s="3" t="b">
         <f>NOT(H19="Intake")</f>
@@ -39109,17 +40227,17 @@
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1144</v>
+        <v>1165</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>A20</f>
@@ -39130,7 +40248,7 @@
         <v>/admin/state-machine/transitions/st-f-04-mechanismconfirmed-to-calibrationchecked</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -39139,19 +40257,19 @@
         <v>519</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="I20" s="2">
         <v>46177.375</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="L20" s="3" t="b">
         <f>NOT(H20="Intake")</f>
@@ -39159,17 +40277,17 @@
       </c>
       <c r="M20" s="6"/>
       <c r="N20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1145</v>
+        <v>1166</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>A21</f>
@@ -39180,7 +40298,7 @@
         <v>/admin/state-machine/transitions/st-f-05-calibrationchecked-to-transportchecked</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -39189,19 +40307,19 @@
         <v>519</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="I21" s="2">
         <v>46178.375</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="L21" s="3" t="b">
         <f>NOT(H21="Intake")</f>
@@ -39209,17 +40327,17 @@
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1146</v>
+        <v>1167</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>A22</f>
@@ -39230,7 +40348,7 @@
         <v>/admin/state-machine/transitions/st-f-06-transportchecked-to-notactionable</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
@@ -39239,19 +40357,19 @@
         <v>519</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="I22" s="2">
         <v>46179.375</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1147</v>
+        <v>1168</v>
       </c>
       <c r="L22" s="3" t="b">
         <f>NOT(H22="Intake")</f>
@@ -39259,17 +40377,17 @@
       </c>
       <c r="M22" s="6"/>
       <c r="N22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>A23</f>
@@ -39280,7 +40398,7 @@
         <v>/admin/state-machine/transitions/st-g-02-intake-to-evidenceassessed</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
@@ -39289,19 +40407,19 @@
         <v>520</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="I23" s="2">
         <v>46175.375</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="L23" s="3" t="b">
         <f>NOT(H23="Intake")</f>
@@ -39309,17 +40427,17 @@
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1149</v>
+        <v>1170</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>A24</f>
@@ -39330,7 +40448,7 @@
         <v>/admin/state-machine/transitions/st-g-03-evidenceassessed-to-mechanismconfirmed</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>10</v>
@@ -39339,19 +40457,19 @@
         <v>520</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="I24" s="2">
         <v>46176.375</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="L24" s="3" t="b">
         <f>NOT(H24="Intake")</f>
@@ -39359,17 +40477,17 @@
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1150</v>
+        <v>1171</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>A25</f>
@@ -39380,7 +40498,7 @@
         <v>/admin/state-machine/transitions/st-g-04-mechanismconfirmed-to-calibrationchecked</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>10</v>
@@ -39389,19 +40507,19 @@
         <v>520</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="I25" s="2">
         <v>46177.375</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="L25" s="3" t="b">
         <f>NOT(H25="Intake")</f>
@@ -39409,17 +40527,17 @@
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>A26</f>
@@ -39430,7 +40548,7 @@
         <v>/admin/state-machine/transitions/st-g-05-calibrationchecked-to-transportchecked</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>10</v>
@@ -39439,19 +40557,19 @@
         <v>520</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="I26" s="2">
         <v>46178.375</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="L26" s="3" t="b">
         <f>NOT(H26="Intake")</f>
@@ -39459,17 +40577,17 @@
       </c>
       <c r="M26" s="6"/>
       <c r="N26" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>1152</v>
+        <v>1173</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>A27</f>
@@ -39480,7 +40598,7 @@
         <v>/admin/state-machine/transitions/st-g-06-transportchecked-to-actionable</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
@@ -39489,19 +40607,19 @@
         <v>520</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="I27" s="2">
         <v>46179.375</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1153</v>
+        <v>1174</v>
       </c>
       <c r="L27" s="3" t="b">
         <f>NOT(H27="Intake")</f>
@@ -39509,11 +40627,11 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q27" s="2"/>
     </row>
@@ -39552,7 +40670,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -39561,57 +40679,57 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1113</v>
+        <v>1134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1155</v>
+        <v>1176</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1156</v>
+        <v>1177</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1158</v>
+        <v>1179</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1160</v>
+        <v>1181</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1161</v>
+        <v>1182</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>A2</f>
@@ -39622,7 +40740,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-intake-1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -39631,7 +40749,7 @@
         <v>513</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H2" s="6">
         <v>46174.375</v>
@@ -39654,17 +40772,17 @@
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>A3</f>
@@ -39675,7 +40793,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-evidenceassessed-2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -39684,7 +40802,7 @@
         <v>513</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H3" s="6">
         <v>46175.375</v>
@@ -39696,10 +40814,10 @@
         <v>2</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="M3" s="3" t="b">
         <f>ISBLANK(I3)</f>
@@ -39711,17 +40829,17 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>A4</f>
@@ -39732,7 +40850,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-mechanismconfirmed-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
@@ -39741,7 +40859,7 @@
         <v>513</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H4" s="6">
         <v>46176.375</v>
@@ -39753,10 +40871,10 @@
         <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1119</v>
+        <v>1140</v>
       </c>
       <c r="M4" s="3" t="b">
         <f>ISBLANK(I4)</f>
@@ -39768,17 +40886,17 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1165</v>
+        <v>1186</v>
       </c>
       <c r="B5" s="3" t="str">
         <f>A5</f>
@@ -39789,7 +40907,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-calibrationchecked-4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
@@ -39798,7 +40916,7 @@
         <v>513</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H5" s="6">
         <v>46177.375</v>
@@ -39810,10 +40928,10 @@
         <v>4</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="M5" s="3" t="b">
         <f>ISBLANK(I5)</f>
@@ -39825,17 +40943,17 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q5" s="6"/>
       <c r="R5" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1166</v>
+        <v>1187</v>
       </c>
       <c r="B6" s="3" t="str">
         <f>A6</f>
@@ -39846,7 +40964,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-transportchecked-5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -39855,7 +40973,7 @@
         <v>513</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H6" s="6">
         <v>46178.375</v>
@@ -39867,10 +40985,10 @@
         <v>5</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>1165</v>
+        <v>1186</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="M6" s="3" t="b">
         <f>ISBLANK(I6)</f>
@@ -39882,17 +41000,17 @@
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1167</v>
+        <v>1188</v>
       </c>
       <c r="B7" s="3" t="str">
         <f>A7</f>
@@ -39903,7 +41021,7 @@
         <v>/admin/state-machine/instances/ssi-pred-a-actionable-6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
@@ -39912,7 +41030,7 @@
         <v>513</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="H7" s="6">
         <v>46179.375</v>
@@ -39922,10 +41040,10 @@
         <v>6</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1166</v>
+        <v>1187</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="M7" s="3" t="b">
         <f>ISBLANK(I7)</f>
@@ -39937,17 +41055,17 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q7" s="6"/>
       <c r="R7" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1168</v>
+        <v>1189</v>
       </c>
       <c r="B8" s="3" t="str">
         <f>A8</f>
@@ -39958,7 +41076,7 @@
         <v>/admin/state-machine/instances/ssi-pred-b-intake-1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
@@ -39967,7 +41085,7 @@
         <v>515</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H8" s="6">
         <v>46174.375</v>
@@ -39990,17 +41108,17 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="B9" s="3" t="str">
         <f>A9</f>
@@ -40011,7 +41129,7 @@
         <v>/admin/state-machine/instances/ssi-pred-b-evidenceassessed-2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
@@ -40020,7 +41138,7 @@
         <v>515</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H9" s="6">
         <v>46175.375</v>
@@ -40032,10 +41150,10 @@
         <v>2</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1168</v>
+        <v>1189</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>1127</v>
+        <v>1148</v>
       </c>
       <c r="M9" s="3" t="b">
         <f>ISBLANK(I9)</f>
@@ -40047,17 +41165,17 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1170</v>
+        <v>1191</v>
       </c>
       <c r="B10" s="3" t="str">
         <f>A10</f>
@@ -40068,7 +41186,7 @@
         <v>/admin/state-machine/instances/ssi-pred-b-mechanismconfirmed-3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -40077,7 +41195,7 @@
         <v>515</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H10" s="6">
         <v>46176.375</v>
@@ -40089,10 +41207,10 @@
         <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1128</v>
+        <v>1149</v>
       </c>
       <c r="M10" s="3" t="b">
         <f>ISBLANK(I10)</f>
@@ -40104,17 +41222,17 @@
       </c>
       <c r="O10" s="6"/>
       <c r="P10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1171</v>
+        <v>1192</v>
       </c>
       <c r="B11" s="3" t="str">
         <f>A11</f>
@@ -40125,7 +41243,7 @@
         <v>/admin/state-machine/instances/ssi-pred-b-calibrationchecked-4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
@@ -40134,7 +41252,7 @@
         <v>515</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H11" s="6">
         <v>46177.375</v>
@@ -40146,10 +41264,10 @@
         <v>4</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>1170</v>
+        <v>1191</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="M11" s="3" t="b">
         <f>ISBLANK(I11)</f>
@@ -40161,17 +41279,17 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1172</v>
+        <v>1193</v>
       </c>
       <c r="B12" s="3" t="str">
         <f>A12</f>
@@ -40182,7 +41300,7 @@
         <v>/admin/state-machine/instances/ssi-pred-b-notactionable-5</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
@@ -40191,7 +41309,7 @@
         <v>515</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="H12" s="6">
         <v>46178.375</v>
@@ -40201,10 +41319,10 @@
         <v>5</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1171</v>
+        <v>1192</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1130</v>
+        <v>1151</v>
       </c>
       <c r="M12" s="3" t="b">
         <f>ISBLANK(I12)</f>
@@ -40216,17 +41334,17 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1173</v>
+        <v>1194</v>
       </c>
       <c r="B13" s="3" t="str">
         <f>A13</f>
@@ -40237,7 +41355,7 @@
         <v>/admin/state-machine/instances/ssi-pred-c-intake-1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
@@ -40246,7 +41364,7 @@
         <v>516</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H13" s="6">
         <v>46174.375</v>
@@ -40269,17 +41387,17 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>1174</v>
+        <v>1195</v>
       </c>
       <c r="B14" s="3" t="str">
         <f>A14</f>
@@ -40290,7 +41408,7 @@
         <v>/admin/state-machine/instances/ssi-pred-c-evidenceassessed-2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
@@ -40299,7 +41417,7 @@
         <v>516</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H14" s="6">
         <v>46175.375</v>
@@ -40311,10 +41429,10 @@
         <v>2</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>1173</v>
+        <v>1194</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1132</v>
+        <v>1153</v>
       </c>
       <c r="M14" s="3" t="b">
         <f>ISBLANK(I14)</f>
@@ -40326,17 +41444,17 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1175</v>
+        <v>1196</v>
       </c>
       <c r="B15" s="3" t="str">
         <f>A15</f>
@@ -40347,7 +41465,7 @@
         <v>/admin/state-machine/instances/ssi-pred-c-notactionable-3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
@@ -40356,7 +41474,7 @@
         <v>516</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="H15" s="6">
         <v>46176.375</v>
@@ -40366,10 +41484,10 @@
         <v>3</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>1174</v>
+        <v>1195</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1133</v>
+        <v>1154</v>
       </c>
       <c r="M15" s="3" t="b">
         <f>ISBLANK(I15)</f>
@@ -40381,17 +41499,17 @@
       </c>
       <c r="O15" s="6"/>
       <c r="P15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1176</v>
+        <v>1197</v>
       </c>
       <c r="B16" s="3" t="str">
         <f>A16</f>
@@ -40402,7 +41520,7 @@
         <v>/admin/state-machine/instances/ssi-pred-d-intake-1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
@@ -40411,7 +41529,7 @@
         <v>517</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H16" s="6">
         <v>46174.375</v>
@@ -40434,17 +41552,17 @@
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1177</v>
+        <v>1198</v>
       </c>
       <c r="B17" s="3" t="str">
         <f>A17</f>
@@ -40455,7 +41573,7 @@
         <v>/admin/state-machine/instances/ssi-pred-d-evidenceassessed-2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
@@ -40464,7 +41582,7 @@
         <v>517</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H17" s="6">
         <v>46175.375</v>
@@ -40476,10 +41594,10 @@
         <v>2</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>1176</v>
+        <v>1197</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="M17" s="3" t="b">
         <f>ISBLANK(I17)</f>
@@ -40491,17 +41609,17 @@
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q17" s="6"/>
       <c r="R17" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>1178</v>
+        <v>1199</v>
       </c>
       <c r="B18" s="3" t="str">
         <f>A18</f>
@@ -40512,7 +41630,7 @@
         <v>/admin/state-machine/instances/ssi-pred-d-mechanismconfirmed-3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
@@ -40521,7 +41639,7 @@
         <v>517</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H18" s="6">
         <v>46176.375</v>
@@ -40533,10 +41651,10 @@
         <v>3</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1177</v>
+        <v>1198</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1136</v>
+        <v>1157</v>
       </c>
       <c r="M18" s="3" t="b">
         <f>ISBLANK(I18)</f>
@@ -40548,17 +41666,17 @@
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>1179</v>
+        <v>1200</v>
       </c>
       <c r="B19" s="3" t="str">
         <f>A19</f>
@@ -40569,7 +41687,7 @@
         <v>/admin/state-machine/instances/ssi-pred-d-notactionable-4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
@@ -40578,7 +41696,7 @@
         <v>517</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="H19" s="6">
         <v>46177.375</v>
@@ -40588,10 +41706,10 @@
         <v>4</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>1178</v>
+        <v>1199</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1137</v>
+        <v>1158</v>
       </c>
       <c r="M19" s="3" t="b">
         <f>ISBLANK(I19)</f>
@@ -40603,17 +41721,17 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q19" s="6"/>
       <c r="R19" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="B20" s="3" t="str">
         <f>A20</f>
@@ -40624,7 +41742,7 @@
         <v>/admin/state-machine/instances/ssi-pred-e-intake-1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
@@ -40633,7 +41751,7 @@
         <v>518</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H20" s="6">
         <v>46174.375</v>
@@ -40656,17 +41774,17 @@
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>1181</v>
+        <v>1202</v>
       </c>
       <c r="B21" s="3" t="str">
         <f>A21</f>
@@ -40677,7 +41795,7 @@
         <v>/admin/state-machine/instances/ssi-pred-e-evidenceassessed-2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
@@ -40686,7 +41804,7 @@
         <v>518</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H21" s="6">
         <v>46175.375</v>
@@ -40698,10 +41816,10 @@
         <v>2</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1139</v>
+        <v>1160</v>
       </c>
       <c r="M21" s="3" t="b">
         <f>ISBLANK(I21)</f>
@@ -40713,17 +41831,17 @@
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>1182</v>
+        <v>1203</v>
       </c>
       <c r="B22" s="3" t="str">
         <f>A22</f>
@@ -40734,7 +41852,7 @@
         <v>/admin/state-machine/instances/ssi-pred-e-notactionable-3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
@@ -40743,7 +41861,7 @@
         <v>518</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="H22" s="6">
         <v>46176.375</v>
@@ -40753,10 +41871,10 @@
         <v>3</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1181</v>
+        <v>1202</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1140</v>
+        <v>1161</v>
       </c>
       <c r="M22" s="3" t="b">
         <f>ISBLANK(I22)</f>
@@ -40768,17 +41886,17 @@
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="B23" s="3" t="str">
         <f>A23</f>
@@ -40789,7 +41907,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-intake-1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>10</v>
@@ -40798,7 +41916,7 @@
         <v>519</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H23" s="6">
         <v>46174.375</v>
@@ -40821,17 +41939,17 @@
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q23" s="6"/>
       <c r="R23" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="B24" s="3" t="str">
         <f>A24</f>
@@ -40842,7 +41960,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-evidenceassessed-2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>10</v>
@@ -40851,7 +41969,7 @@
         <v>519</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H24" s="6">
         <v>46175.375</v>
@@ -40863,10 +41981,10 @@
         <v>2</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1142</v>
+        <v>1163</v>
       </c>
       <c r="M24" s="3" t="b">
         <f>ISBLANK(I24)</f>
@@ -40878,17 +41996,17 @@
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>1185</v>
+        <v>1206</v>
       </c>
       <c r="B25" s="3" t="str">
         <f>A25</f>
@@ -40899,7 +42017,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-mechanismconfirmed-3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>10</v>
@@ -40908,7 +42026,7 @@
         <v>519</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H25" s="6">
         <v>46176.375</v>
@@ -40920,10 +42038,10 @@
         <v>3</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="M25" s="3" t="b">
         <f>ISBLANK(I25)</f>
@@ -40935,17 +42053,17 @@
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q25" s="6"/>
       <c r="R25" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>1186</v>
+        <v>1207</v>
       </c>
       <c r="B26" s="3" t="str">
         <f>A26</f>
@@ -40956,7 +42074,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-calibrationchecked-4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>10</v>
@@ -40965,7 +42083,7 @@
         <v>519</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H26" s="6">
         <v>46177.375</v>
@@ -40977,10 +42095,10 @@
         <v>4</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>1185</v>
+        <v>1206</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1144</v>
+        <v>1165</v>
       </c>
       <c r="M26" s="3" t="b">
         <f>ISBLANK(I26)</f>
@@ -40992,17 +42110,17 @@
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>1187</v>
+        <v>1208</v>
       </c>
       <c r="B27" s="3" t="str">
         <f>A27</f>
@@ -41013,7 +42131,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-transportchecked-5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>10</v>
@@ -41022,7 +42140,7 @@
         <v>519</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H27" s="6">
         <v>46178.375</v>
@@ -41034,10 +42152,10 @@
         <v>5</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>1186</v>
+        <v>1207</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1145</v>
+        <v>1166</v>
       </c>
       <c r="M27" s="3" t="b">
         <f>ISBLANK(I27)</f>
@@ -41049,17 +42167,17 @@
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q27" s="6"/>
       <c r="R27" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>1188</v>
+        <v>1209</v>
       </c>
       <c r="B28" s="3" t="str">
         <f>A28</f>
@@ -41070,7 +42188,7 @@
         <v>/admin/state-machine/instances/ssi-pred-f-notactionable-6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>10</v>
@@ -41079,7 +42197,7 @@
         <v>519</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="H28" s="6">
         <v>46179.375</v>
@@ -41089,10 +42207,10 @@
         <v>6</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1187</v>
+        <v>1208</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1146</v>
+        <v>1167</v>
       </c>
       <c r="M28" s="3" t="b">
         <f>ISBLANK(I28)</f>
@@ -41104,17 +42222,17 @@
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>1189</v>
+        <v>1210</v>
       </c>
       <c r="B29" s="3" t="str">
         <f>A29</f>
@@ -41125,7 +42243,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-intake-1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>10</v>
@@ -41134,7 +42252,7 @@
         <v>520</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H29" s="6">
         <v>46174.375</v>
@@ -41157,17 +42275,17 @@
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q29" s="6"/>
       <c r="R29" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="B30" s="3" t="str">
         <f>A30</f>
@@ -41178,7 +42296,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-evidenceassessed-2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>10</v>
@@ -41187,7 +42305,7 @@
         <v>520</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="H30" s="6">
         <v>46175.375</v>
@@ -41199,10 +42317,10 @@
         <v>2</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>1189</v>
+        <v>1210</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="M30" s="3" t="b">
         <f>ISBLANK(I30)</f>
@@ -41214,17 +42332,17 @@
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>1191</v>
+        <v>1212</v>
       </c>
       <c r="B31" s="3" t="str">
         <f>A31</f>
@@ -41235,7 +42353,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-mechanismconfirmed-3</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>10</v>
@@ -41244,7 +42362,7 @@
         <v>520</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H31" s="6">
         <v>46176.375</v>
@@ -41256,10 +42374,10 @@
         <v>3</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1149</v>
+        <v>1170</v>
       </c>
       <c r="M31" s="3" t="b">
         <f>ISBLANK(I31)</f>
@@ -41271,17 +42389,17 @@
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="B32" s="3" t="str">
         <f>A32</f>
@@ -41292,7 +42410,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-calibrationchecked-4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>10</v>
@@ -41301,7 +42419,7 @@
         <v>520</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="H32" s="6">
         <v>46177.375</v>
@@ -41313,10 +42431,10 @@
         <v>4</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1191</v>
+        <v>1212</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1150</v>
+        <v>1171</v>
       </c>
       <c r="M32" s="3" t="b">
         <f>ISBLANK(I32)</f>
@@ -41328,17 +42446,17 @@
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="B33" s="3" t="str">
         <f>A33</f>
@@ -41349,7 +42467,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-transportchecked-5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>10</v>
@@ -41358,7 +42476,7 @@
         <v>520</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="H33" s="6">
         <v>46178.375</v>
@@ -41370,10 +42488,10 @@
         <v>5</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="M33" s="3" t="b">
         <f>ISBLANK(I33)</f>
@@ -41385,17 +42503,17 @@
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q33" s="6"/>
       <c r="R33" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>1194</v>
+        <v>1215</v>
       </c>
       <c r="B34" s="3" t="str">
         <f>A34</f>
@@ -41406,7 +42524,7 @@
         <v>/admin/state-machine/instances/ssi-pred-g-actionable-6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>10</v>
@@ -41415,7 +42533,7 @@
         <v>520</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="H34" s="6">
         <v>46179.375</v>
@@ -41425,10 +42543,10 @@
         <v>6</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1152</v>
+        <v>1173</v>
       </c>
       <c r="M34" s="3" t="b">
         <f>ISBLANK(I34)</f>
@@ -41440,11 +42558,11 @@
       </c>
       <c r="O34" s="6"/>
       <c r="P34" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="S34" s="2"/>
     </row>
@@ -41462,22 +42580,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1195</v>
+        <v>1216</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>591</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1196</v>
+        <v>1217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1197</v>
+        <v>1218</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>688</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1198</v>
+        <v>1219</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -41488,22 +42606,22 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>1199</v>
+        <v>1220</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1203</v>
+        <v>1224</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>A2</f>
@@ -41516,22 +42634,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>1205</v>
+        <v>1226</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1206</v>
+        <v>1227</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1207</v>
+        <v>1228</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>A3</f>
@@ -41544,22 +42662,22 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>1208</v>
+        <v>1229</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1209</v>
+        <v>1230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1210</v>
+        <v>1231</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1211</v>
+        <v>1232</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>A4</f>
@@ -41572,22 +42690,22 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1213</v>
+        <v>1234</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1214</v>
+        <v>1235</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1215</v>
+        <v>1236</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="G5" s="3" t="str">
         <f>A5</f>
@@ -41600,22 +42718,22 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>1216</v>
+        <v>1237</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1218</v>
+        <v>1239</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1219</v>
+        <v>1240</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>A6</f>
@@ -41628,22 +42746,22 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>1221</v>
+        <v>1242</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1222</v>
+        <v>1243</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1223</v>
+        <v>1244</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G7" s="3" t="str">
         <f>A7</f>
@@ -41656,22 +42774,22 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>1224</v>
+        <v>1245</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1225</v>
+        <v>1246</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1226</v>
+        <v>1247</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>A8</f>
@@ -41684,22 +42802,22 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>1227</v>
+        <v>1248</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1228</v>
+        <v>1249</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="G9" s="3" t="str">
         <f>A9</f>
@@ -41712,22 +42830,22 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>1230</v>
+        <v>1251</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1232</v>
+        <v>1253</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1235</v>
+        <v>1256</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>A10</f>
@@ -41740,22 +42858,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>1236</v>
+        <v>1257</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1237</v>
+        <v>1258</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1238</v>
+        <v>1259</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1235</v>
+        <v>1256</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>A11</f>
@@ -41768,22 +42886,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>1239</v>
+        <v>1260</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1240</v>
+        <v>1261</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1241</v>
+        <v>1262</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1235</v>
+        <v>1256</v>
       </c>
       <c r="G12" s="3" t="str">
         <f>A12</f>
@@ -41796,22 +42914,22 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>1242</v>
+        <v>1263</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1244</v>
+        <v>1265</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1245</v>
+        <v>1266</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G13" s="3" t="str">
         <f>A13</f>
@@ -41824,22 +42942,22 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>1246</v>
+        <v>1267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G14" s="3" t="str">
         <f>A14</f>
@@ -41852,22 +42970,22 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>1249</v>
+        <v>1270</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
       <c r="G15" s="3" t="str">
         <f>A15</f>
@@ -41880,22 +42998,22 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1213</v>
+        <v>1234</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1214</v>
+        <v>1235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1254</v>
+        <v>1275</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="G16" s="3" t="str">
         <f>A16</f>
@@ -41908,22 +43026,22 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>1255</v>
+        <v>1276</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1253</v>
+        <v>1274</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1213</v>
+        <v>1234</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1214</v>
+        <v>1235</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1256</v>
+        <v>1277</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="G17" s="3" t="str">
         <f>A17</f>
@@ -41943,80 +43061,1077 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.739782333374023" customWidth="1"/>
+    <col min="2" max="2" width="42.18617630004883" customWidth="1"/>
+    <col min="3" max="3" width="17.443378448486328" customWidth="1"/>
+    <col min="4" max="4" width="17.443378448486328" customWidth="1"/>
+    <col min="5" max="5" width="184.0491180419922" customWidth="1"/>
+    <col min="6" max="6" width="69.81665802001953" customWidth="1"/>
+    <col min="7" max="7" width="42.18617630004883" customWidth="1"/>
+    <col min="8" max="8" width="52.031272888183594" customWidth="1"/>
+    <col min="9" max="9" width="17.656658172607422" customWidth="1"/>
+    <col min="10" max="10" width="18.580236434936523" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G2" s="3" t="str">
+        <f>B2</f>
+        <v>Lupus Nephritis</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A2</f>
+        <v>/admin/disease-concepts/lupus-nephritis</v>
+      </c>
+      <c r="I2" s="3" t="b">
+        <f>IF(D2="deep-dag", TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="b">
+        <f>IF(OR(D2="deep-dag",D2="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f>B3</f>
+        <v>Treatment-Line Selection</v>
+      </c>
+      <c r="H3" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A3</f>
+        <v>/admin/disease-concepts/treatment-line-selection</v>
+      </c>
+      <c r="I3" s="3" t="b">
+        <f>IF(D3="deep-dag", TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="b">
+        <f>IF(OR(D3="deep-dag",D3="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f>B4</f>
+        <v>Neuropsychiatric Lupus (NPSLE)</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A4</f>
+        <v>/admin/disease-concepts/neuropsychiatric-lupus</v>
+      </c>
+      <c r="I4" s="3" t="b">
+        <f>IF(D4="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="b">
+        <f>IF(OR(D4="deep-dag",D4="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f>B5</f>
+        <v>Cutaneous Lupus</v>
+      </c>
+      <c r="H5" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A5</f>
+        <v>/admin/disease-concepts/cutaneous-lupus</v>
+      </c>
+      <c r="I5" s="3" t="b">
+        <f>IF(D5="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="b">
+        <f>IF(OR(D5="deep-dag",D5="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f>B6</f>
+        <v>Organ Damage (SLICC/ACR Damage Index)</v>
+      </c>
+      <c r="H6" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A6</f>
+        <v>/admin/disease-concepts/organ-damage-slicc</v>
+      </c>
+      <c r="I6" s="3" t="b">
+        <f>IF(D6="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <f>IF(OR(D6="deep-dag",D6="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f>B7</f>
+        <v>Seropositive RA (ACPA/RF+)</v>
+      </c>
+      <c r="H7" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A7</f>
+        <v>/admin/disease-concepts/seropositive-ra</v>
+      </c>
+      <c r="I7" s="3" t="b">
+        <f>IF(D7="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="b">
+        <f>IF(OR(D7="deep-dag",D7="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <f>B8</f>
+        <v>Seronegative RA (ACPA/RF-)</v>
+      </c>
+      <c r="H8" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A8</f>
+        <v>/admin/disease-concepts/seronegative-ra</v>
+      </c>
+      <c r="I8" s="3" t="b">
+        <f>IF(D8="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="b">
+        <f>IF(OR(D8="deep-dag",D8="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f>B9</f>
+        <v>Erosive Disease</v>
+      </c>
+      <c r="H9" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A9</f>
+        <v>/admin/disease-concepts/erosive-disease</v>
+      </c>
+      <c r="I9" s="3" t="b">
+        <f>IF(D9="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <f>IF(OR(D9="deep-dag",D9="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f>B10</f>
+        <v>Axial Psoriatic Arthritis</v>
+      </c>
+      <c r="H10" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A10</f>
+        <v>/admin/disease-concepts/axial-psa</v>
+      </c>
+      <c r="I10" s="3" t="b">
+        <f>IF(D10="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <f>IF(OR(D10="deep-dag",D10="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f>B11</f>
+        <v>Enthesitis</v>
+      </c>
+      <c r="H11" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A11</f>
+        <v>/admin/disease-concepts/enthesitis</v>
+      </c>
+      <c r="I11" s="3" t="b">
+        <f>IF(D11="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="b">
+        <f>IF(OR(D11="deep-dag",D11="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f>B12</f>
+        <v>Dactylitis</v>
+      </c>
+      <c r="H12" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A12</f>
+        <v>/admin/disease-concepts/dactylitis</v>
+      </c>
+      <c r="I12" s="3" t="b">
+        <f>IF(D12="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="b">
+        <f>IF(OR(D12="deep-dag",D12="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f>B13</f>
+        <v>Uveitis</v>
+      </c>
+      <c r="H13" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A13</f>
+        <v>/admin/disease-concepts/uveitis</v>
+      </c>
+      <c r="I13" s="3" t="b">
+        <f>IF(D13="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="b">
+        <f>IF(OR(D13="deep-dag",D13="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f>B14</f>
+        <v>Inflammatory Bowel Disease Overlap</v>
+      </c>
+      <c r="H14" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A14</f>
+        <v>/admin/disease-concepts/ibd-overlap</v>
+      </c>
+      <c r="I14" s="3" t="b">
+        <f>IF(D14="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="b">
+        <f>IF(OR(D14="deep-dag",D14="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f>B15</f>
+        <v>Flare Pattern</v>
+      </c>
+      <c r="H15" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A15</f>
+        <v>/admin/disease-concepts/flare-pattern</v>
+      </c>
+      <c r="I15" s="3" t="b">
+        <f>IF(D15="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <f>IF(OR(D15="deep-dag",D15="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <f>B16</f>
+        <v>Disease-Activity Score (SLEDAI / DAS28)</v>
+      </c>
+      <c r="H16" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A16</f>
+        <v>/admin/disease-concepts/disease-activity-score</v>
+      </c>
+      <c r="I16" s="3" t="b">
+        <f>IF(D16="deep-dag", TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <f>IF(OR(D16="deep-dag",D16="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f>B17</f>
+        <v>Treatment Line</v>
+      </c>
+      <c r="H17" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A17</f>
+        <v>/admin/disease-concepts/treatment-line</v>
+      </c>
+      <c r="I17" s="3" t="b">
+        <f>IF(D17="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="b">
+        <f>IF(OR(D17="deep-dag",D17="schema"), TRUE(), FALSE())</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f>B18</f>
+        <v>Adverse-Event Surveillance</v>
+      </c>
+      <c r="H18" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A18</f>
+        <v>/admin/disease-concepts/adverse-event-surveillance</v>
+      </c>
+      <c r="I18" s="3" t="b">
+        <f>IF(D18="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="b">
+        <f>IF(OR(D18="deep-dag",D18="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f>B19</f>
+        <v>Workflow: Referral</v>
+      </c>
+      <c r="H19" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A19</f>
+        <v>/admin/disease-concepts/workflow-referral</v>
+      </c>
+      <c r="I19" s="3" t="b">
+        <f>IF(D19="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="b">
+        <f>IF(OR(D19="deep-dag",D19="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f>B20</f>
+        <v>Workflow: Differential Diagnosis</v>
+      </c>
+      <c r="H20" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A20</f>
+        <v>/admin/disease-concepts/workflow-differential</v>
+      </c>
+      <c r="I20" s="3" t="b">
+        <f>IF(D20="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="b">
+        <f>IF(OR(D20="deep-dag",D20="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f>B21</f>
+        <v>Workflow: Workup</v>
+      </c>
+      <c r="H21" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A21</f>
+        <v>/admin/disease-concepts/workflow-workup</v>
+      </c>
+      <c r="I21" s="3" t="b">
+        <f>IF(D21="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="b">
+        <f>IF(OR(D21="deep-dag",D21="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f>B22</f>
+        <v>Workflow: Classification</v>
+      </c>
+      <c r="H22" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A22</f>
+        <v>/admin/disease-concepts/workflow-classification</v>
+      </c>
+      <c r="I22" s="3" t="b">
+        <f>IF(D22="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="b">
+        <f>IF(OR(D22="deep-dag",D22="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f>B23</f>
+        <v>Workflow: Baseline Severity Assessment</v>
+      </c>
+      <c r="H23" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A23</f>
+        <v>/admin/disease-concepts/workflow-baseline-severity</v>
+      </c>
+      <c r="I23" s="3" t="b">
+        <f>IF(D23="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="b">
+        <f>IF(OR(D23="deep-dag",D23="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>B24</f>
+        <v>Workflow: Treatment Choice</v>
+      </c>
+      <c r="H24" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A24</f>
+        <v>/admin/disease-concepts/workflow-treatment-choice</v>
+      </c>
+      <c r="I24" s="3" t="b">
+        <f>IF(D24="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="b">
+        <f>IF(OR(D24="deep-dag",D24="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>B25</f>
+        <v>Workflow: Monitoring</v>
+      </c>
+      <c r="H25" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A25</f>
+        <v>/admin/disease-concepts/workflow-monitoring</v>
+      </c>
+      <c r="I25" s="3" t="b">
+        <f>IF(D25="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="b">
+        <f>IF(OR(D25="deep-dag",D25="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>B26</f>
+        <v>Workflow: Flare Management</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A26</f>
+        <v>/admin/disease-concepts/workflow-flare-management</v>
+      </c>
+      <c r="I26" s="3" t="b">
+        <f>IF(D26="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="b">
+        <f>IF(OR(D26="deep-dag",D26="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>B27</f>
+        <v>Workflow: Long-Term Outcomes</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f>"/admin/disease-concepts/" &amp; A27</f>
+        <v>/admin/disease-concepts/workflow-outcomes</v>
+      </c>
+      <c r="I27" s="3" t="b">
+        <f>IF(D27="deep-dag", TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="b">
+        <f>IF(OR(D27="deep-dag",D27="schema"), TRUE(), FALSE())</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>1257</v>
+        <v>1390</v>
       </c>
       <c r="Z1" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1258</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1259</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1260</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1261</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1262</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1263</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1264</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1265</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1266</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1267</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1268</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1269</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1270</v>
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>1404</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/causal-autoimmune-architecture-platform.xlsx
+++ b/xlsx/causal-autoimmune-architecture-platform.xlsx
@@ -11309,7 +11309,7 @@
     <t>nav-admin-cohort</t>
   </si>
   <si>
-    <t>Cohort</t>
+    <t>Cohort discovery</t>
   </si>
   <si>
     <t>/admin/cohort</t>
@@ -21522,10 +21522,10 @@
       },
       {
         "RoutingAndNavigationId": "nav-admin-cohort",
-        "DisplayName": "Cohort",
+        "DisplayName": "Cohort discovery",
         "Route": "/admin/cohort",
         "Description": "All 7 cases and their keystone verdicts.",
-        "SortOrder": 95,
+        "SortOrder": 91.5,
         "ParentRouteKey": "admin",
         "RouteKey": "admin.cohort",
         "NavLevel": "sub",
@@ -22385,10 +22385,10 @@
         "ToState": "diagnosis-lifecycle--notactionable",
         "GuardDescription": "Cryptic-relatedness leakage \u21d2 HasSpuriousCorrelationFlag.",
         "TriggeredByRole": "system",
-        "CreatedBy":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "build-seed",
+        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"CreatedBy": "build-seed",
         "ModifiedBy": "build-seed",
         "Name": "diagnosis-lifecycle--mechanismconfirmed-&gt;notactionable",
         "RelativePath": "/admin/state-machine/rules/diagnosis-lifecycle--mechanismconfirmed-&gt;notactionable",
@@ -23183,10 +23183,10 @@
         "ToStateKey": "Actionable",
         "TransitionAt": "2026-06-06T09:00:00Z",
         "TriggeredByRole": "system",
-        "Reason": "transport passes \u2014 actionable de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spite holdout.",
+        "Reason": "transport passes \u2014 a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctionable despite holdout.",
         "CreatedBy": "build-seed",
         "ModifiedBy": "build-seed",
         "Name": "st-g-06-transportchecked-to-actionable",
@@ -24008,10 +24008,10 @@
         "CreatedBy": "build-seed",
         "ModifiedBy": "build-seed",
         "Name": "ssi-pred-d-notactionable-4",
-        "RelativePath": "/admin/stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-machine/instances/ssi-pred-d-notactionable-4",
+        "RelativePath": </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"/admin/state-machine/instances/ssi-pred-d-notactionable-4",
         "IsCurrent": true,
         "HasCompleteLineage": true,
         "CreatedAt": null,
@@ -24780,10 +24780,10 @@
       },
       {
         "MetaKey": "band.temperature.fever-high",
-        "Category": "ba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nd-threshold",
+        "Ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tegory": "band-threshold",
         "Value": "100.5",
         "ValueType": "number",
         "Description": "Upper bound (degF) of the 'light fever' band; strictly above this is a 'severe fever'.",
@@ -25554,10 +25554,10 @@
         "ComplementC3": 70,
         "ComplementC4": 10,
         "ProteinuriaGPerDay": 0.3,
-        "EgfrMlMin":</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 90,
+        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"EgfrMlMin": 90,
         "HasActiveUrinarySediment": false,
         "PriorObservation": "sero-ind-c-chen-1",
         "Name": "sero-ind-c-chen-2",
@@ -40855,7 +40855,7 @@
       </c>
       <c r="B23" s="3" t="str">
         <f>SUBSTITUTE(LOWER(C23), " ", "-")</f>
-        <v>cohort</v>
+        <v>cohort-discovery</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>1086</v>
@@ -40867,7 +40867,7 @@
         <v>1088</v>
       </c>
       <c r="F23" s="2">
-        <v>95</v>
+        <v>91.5</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>1055</v>
